--- a/لیست_قیمت_وایر عباسی.xlsx
+++ b/لیست_قیمت_وایر عباسی.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaser\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A338537-0A43-42A3-9A5B-F035A3484712}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9525"/>
   </bookViews>
   <sheets>
     <sheet name="لیست کالاها" sheetId="1" r:id="rId1"/>
@@ -24,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="190">
   <si>
     <t>کد کالا</t>
   </si>
@@ -455,146 +449,152 @@
     <t>تمام سیلیکون سه لایه نمره کابل تقویتی 8 و استیل 7.5 واقعی</t>
   </si>
   <si>
-    <t>8234000</t>
-  </si>
-  <si>
-    <t>6848000</t>
-  </si>
-  <si>
-    <t>8333000</t>
-  </si>
-  <si>
-    <t>7013000</t>
-  </si>
-  <si>
     <t>7920000</t>
   </si>
   <si>
-    <t>6683000</t>
-  </si>
-  <si>
-    <t>9884000</t>
-  </si>
-  <si>
-    <t>7590000</t>
-  </si>
-  <si>
-    <t>6353000</t>
-  </si>
-  <si>
-    <t>7508000</t>
-  </si>
-  <si>
-    <t>7178000</t>
-  </si>
-  <si>
-    <t>8663000</t>
-  </si>
-  <si>
-    <t>9488000</t>
-  </si>
-  <si>
-    <t>5693000</t>
-  </si>
-  <si>
-    <t>8828000</t>
-  </si>
-  <si>
-    <t>8745000</t>
-  </si>
-  <si>
-    <t>7623000</t>
-  </si>
-  <si>
-    <t>7838000</t>
-  </si>
-  <si>
-    <t>9405000</t>
-  </si>
-  <si>
-    <t>8168000</t>
-  </si>
-  <si>
-    <t>6881000</t>
-  </si>
-  <si>
-    <t>8531000</t>
-  </si>
-  <si>
-    <t>2310000</t>
-  </si>
-  <si>
-    <t>2228000</t>
-  </si>
-  <si>
-    <t>2805000</t>
-  </si>
-  <si>
-    <t>2849000</t>
-  </si>
-  <si>
-    <t>2970000</t>
-  </si>
-  <si>
-    <t>10478000</t>
-  </si>
-  <si>
-    <t>10560000</t>
-  </si>
-  <si>
-    <t>9075000</t>
-  </si>
-  <si>
-    <t>8910000</t>
-  </si>
-  <si>
-    <t>6600000</t>
-  </si>
-  <si>
-    <t>2888000</t>
-  </si>
-  <si>
-    <t>2475000</t>
-  </si>
-  <si>
-    <t>9471000</t>
-  </si>
-  <si>
-    <t>9295000</t>
-  </si>
-  <si>
-    <t>8833000</t>
-  </si>
-  <si>
-    <t>10010000</t>
-  </si>
-  <si>
-    <t>10087000</t>
-  </si>
-  <si>
-    <t>10549000</t>
-  </si>
-  <si>
-    <t>10857000</t>
-  </si>
-  <si>
-    <t>11429000</t>
-  </si>
-  <si>
-    <t>8140000</t>
-  </si>
-  <si>
-    <t>10153000</t>
-  </si>
-  <si>
-    <t>6435000</t>
+    <t>9440000</t>
+  </si>
+  <si>
+    <t>4350000</t>
+  </si>
+  <si>
+    <t>11560000</t>
+  </si>
+  <si>
+    <t>13550000</t>
+  </si>
+  <si>
+    <t>12670000</t>
+  </si>
+  <si>
+    <t>10110000</t>
+  </si>
+  <si>
+    <t>13160000</t>
+  </si>
+  <si>
+    <t>12500000</t>
+  </si>
+  <si>
+    <t>14300000</t>
+  </si>
+  <si>
+    <t>4600000</t>
+  </si>
+  <si>
+    <t>12590000</t>
+  </si>
+  <si>
+    <t>10960000</t>
+  </si>
+  <si>
+    <t>11800000</t>
+  </si>
+  <si>
+    <t>4590000</t>
+  </si>
+  <si>
+    <t>8510000</t>
+  </si>
+  <si>
+    <t>10210000</t>
+  </si>
+  <si>
+    <t>9300000</t>
+  </si>
+  <si>
+    <t>11610000</t>
+  </si>
+  <si>
+    <t>12200000</t>
+  </si>
+  <si>
+    <t>3550000</t>
+  </si>
+  <si>
+    <t>3420000</t>
+  </si>
+  <si>
+    <t>3300000</t>
+  </si>
+  <si>
+    <t>10730000</t>
+  </si>
+  <si>
+    <t>8830000</t>
+  </si>
+  <si>
+    <t>10850000</t>
+  </si>
+  <si>
+    <t>9060000</t>
+  </si>
+  <si>
+    <t>10300000</t>
+  </si>
+  <si>
+    <t>8620000</t>
+  </si>
+  <si>
+    <t>12890000</t>
+  </si>
+  <si>
+    <t>10530000</t>
+  </si>
+  <si>
+    <t>9900000</t>
+  </si>
+  <si>
+    <t>8230000</t>
+  </si>
+  <si>
+    <t>9720000</t>
+  </si>
+  <si>
+    <t>8210000</t>
+  </si>
+  <si>
+    <t>11260000</t>
+  </si>
+  <si>
+    <t>9350000</t>
+  </si>
+  <si>
+    <t>13720000</t>
+  </si>
+  <si>
+    <t>12430000</t>
+  </si>
+  <si>
+    <t>8900000</t>
+  </si>
+  <si>
+    <t>7360000</t>
+  </si>
+  <si>
+    <t>13800000</t>
+  </si>
+  <si>
+    <t>11310000</t>
+  </si>
+  <si>
+    <t>9850000</t>
+  </si>
+  <si>
+    <t>11810000</t>
+  </si>
+  <si>
+    <t>12300000</t>
+  </si>
+  <si>
+    <t>11030000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -701,7 +701,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -733,27 +733,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -785,24 +767,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -978,9 +942,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2001"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -988,7 +952,7 @@
     <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1002,7 +966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1010,13 +974,13 @@
         <v>76</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -1024,13 +988,13 @@
         <v>77</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -1038,13 +1002,13 @@
         <v>78</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -1052,13 +1016,13 @@
         <v>79</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -1066,13 +1030,13 @@
         <v>80</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -1080,13 +1044,13 @@
         <v>81</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -1094,13 +1058,13 @@
         <v>82</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1108,13 +1072,13 @@
         <v>83</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1122,13 +1086,13 @@
         <v>84</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1136,13 +1100,13 @@
         <v>85</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
@@ -1150,13 +1114,13 @@
         <v>86</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -1164,13 +1128,13 @@
         <v>87</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -1178,13 +1142,13 @@
         <v>88</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
@@ -1192,13 +1156,13 @@
         <v>89</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -1206,13 +1170,13 @@
         <v>90</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
@@ -1220,13 +1184,13 @@
         <v>91</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
@@ -1234,13 +1198,13 @@
         <v>92</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
@@ -1248,13 +1212,13 @@
         <v>93</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
         <v>28</v>
       </c>
@@ -1262,13 +1226,13 @@
         <v>94</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
         <v>29</v>
       </c>
@@ -1276,13 +1240,13 @@
         <v>95</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
         <v>30</v>
       </c>
@@ -1290,13 +1254,13 @@
         <v>96</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
         <v>31</v>
       </c>
@@ -1304,13 +1268,13 @@
         <v>97</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
         <v>32</v>
       </c>
@@ -1318,13 +1282,13 @@
         <v>98</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
         <v>33</v>
       </c>
@@ -1332,13 +1296,13 @@
         <v>99</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
         <v>34</v>
       </c>
@@ -1346,13 +1310,13 @@
         <v>100</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
         <v>35</v>
       </c>
@@ -1360,13 +1324,13 @@
         <v>101</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
         <v>36</v>
       </c>
@@ -1374,13 +1338,13 @@
         <v>102</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
         <v>37</v>
       </c>
@@ -1388,13 +1352,13 @@
         <v>103</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
         <v>38</v>
       </c>
@@ -1402,13 +1366,13 @@
         <v>104</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
         <v>39</v>
       </c>
@@ -1416,13 +1380,13 @@
         <v>105</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
         <v>40</v>
       </c>
@@ -1430,13 +1394,13 @@
         <v>106</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33" s="4" t="s">
         <v>41</v>
       </c>
@@ -1444,13 +1408,13 @@
         <v>107</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34" s="4" t="s">
         <v>42</v>
       </c>
@@ -1458,13 +1422,13 @@
         <v>108</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -1472,13 +1436,13 @@
         <v>109</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
         <v>44</v>
       </c>
@@ -1492,7 +1456,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
         <v>45</v>
       </c>
@@ -1506,7 +1470,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4">
       <c r="A38" s="4" t="s">
         <v>46</v>
       </c>
@@ -1520,7 +1484,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
         <v>47</v>
       </c>
@@ -1528,13 +1492,13 @@
         <v>113</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
         <v>48</v>
       </c>
@@ -1542,13 +1506,13 @@
         <v>114</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
         <v>49</v>
       </c>
@@ -1556,13 +1520,13 @@
         <v>115</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4">
       <c r="A42" s="4" t="s">
         <v>50</v>
       </c>
@@ -1570,13 +1534,13 @@
         <v>116</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4">
       <c r="A43" s="4" t="s">
         <v>51</v>
       </c>
@@ -1584,13 +1548,13 @@
         <v>117</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
         <v>52</v>
       </c>
@@ -1598,13 +1562,13 @@
         <v>118</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4">
       <c r="A45" s="4" t="s">
         <v>53</v>
       </c>
@@ -1612,13 +1576,13 @@
         <v>119</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4">
       <c r="A46" s="4" t="s">
         <v>54</v>
       </c>
@@ -1626,13 +1590,13 @@
         <v>120</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
         <v>55</v>
       </c>
@@ -1640,13 +1604,13 @@
         <v>121</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4">
       <c r="A48" s="4" t="s">
         <v>56</v>
       </c>
@@ -1654,13 +1618,13 @@
         <v>122</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4">
       <c r="A49" s="4" t="s">
         <v>57</v>
       </c>
@@ -1668,13 +1632,13 @@
         <v>123</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4">
       <c r="A50" s="4" t="s">
         <v>58</v>
       </c>
@@ -1682,13 +1646,13 @@
         <v>124</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4">
       <c r="A51" s="4" t="s">
         <v>59</v>
       </c>
@@ -1696,13 +1660,13 @@
         <v>125</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4">
       <c r="A52" s="4" t="s">
         <v>60</v>
       </c>
@@ -1710,13 +1674,13 @@
         <v>126</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4">
       <c r="A53" s="4" t="s">
         <v>61</v>
       </c>
@@ -1724,13 +1688,13 @@
         <v>127</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4">
       <c r="A54" s="4" t="s">
         <v>62</v>
       </c>
@@ -1738,13 +1702,13 @@
         <v>128</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4">
       <c r="A55" s="4" t="s">
         <v>63</v>
       </c>
@@ -1752,13 +1716,13 @@
         <v>129</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4">
       <c r="A56" s="4" t="s">
         <v>64</v>
       </c>
@@ -1766,13 +1730,13 @@
         <v>130</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4">
       <c r="A57" s="4" t="s">
         <v>65</v>
       </c>
@@ -1780,13 +1744,13 @@
         <v>131</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4">
       <c r="A58" s="4" t="s">
         <v>66</v>
       </c>
@@ -1794,13 +1758,13 @@
         <v>132</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4">
       <c r="A59" s="4" t="s">
         <v>67</v>
       </c>
@@ -1808,13 +1772,13 @@
         <v>133</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4">
       <c r="A60" s="4" t="s">
         <v>68</v>
       </c>
@@ -1822,13 +1786,13 @@
         <v>134</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4">
       <c r="A61" s="4" t="s">
         <v>69</v>
       </c>
@@ -1836,13 +1800,13 @@
         <v>135</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4">
       <c r="A62" s="4" t="s">
         <v>70</v>
       </c>
@@ -1850,13 +1814,13 @@
         <v>136</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4">
       <c r="A63" s="4" t="s">
         <v>71</v>
       </c>
@@ -1864,13 +1828,13 @@
         <v>137</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4">
       <c r="A64" s="4" t="s">
         <v>72</v>
       </c>
@@ -1878,13 +1842,13 @@
         <v>138</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4">
       <c r="A65" s="4" t="s">
         <v>73</v>
       </c>
@@ -1892,13 +1856,13 @@
         <v>139</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4">
       <c r="A66" s="4" t="s">
         <v>74</v>
       </c>
@@ -1906,13 +1870,13 @@
         <v>140</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4">
       <c r="A67" s="4" t="s">
         <v>75</v>
       </c>
@@ -1920,5854 +1884,5858 @@
         <v>141</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4">
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4">
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4">
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4">
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4">
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4">
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4">
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4">
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4">
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4">
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4">
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4">
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4">
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:3">
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:3">
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:3">
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:3">
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:3">
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:3">
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:3">
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:3">
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:3">
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:3">
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:3">
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:3">
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:3">
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:3">
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:3">
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:3">
       <c r="C96" s="2"/>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:3">
       <c r="C97" s="2"/>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:3">
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:3">
       <c r="C99" s="2"/>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:3">
       <c r="C100" s="2"/>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:3">
       <c r="C101" s="2"/>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:3">
       <c r="C102" s="2"/>
     </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:3">
       <c r="C103" s="2"/>
     </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:3">
       <c r="C104" s="2"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:3">
       <c r="C105" s="2"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:3">
       <c r="C106" s="2"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:3">
       <c r="C107" s="2"/>
     </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:3">
       <c r="C108" s="2"/>
     </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:3">
       <c r="C109" s="2"/>
     </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:3">
       <c r="C110" s="2"/>
     </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:3">
       <c r="C111" s="2"/>
     </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:3">
       <c r="C112" s="2"/>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:3">
       <c r="C113" s="2"/>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:3">
       <c r="C114" s="2"/>
     </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:3">
       <c r="C115" s="2"/>
     </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:3">
       <c r="C116" s="2"/>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:3">
       <c r="C117" s="2"/>
     </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:3">
       <c r="C118" s="2"/>
     </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:3">
       <c r="C119" s="2"/>
     </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:3">
       <c r="C120" s="2"/>
     </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:3">
       <c r="C121" s="2"/>
     </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:3">
       <c r="C122" s="2"/>
     </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:3">
       <c r="C123" s="2"/>
     </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:3">
       <c r="C124" s="2"/>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:3">
       <c r="C125" s="2"/>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:3">
       <c r="C126" s="2"/>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:3">
       <c r="C127" s="2"/>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:3">
       <c r="C128" s="2"/>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:3">
       <c r="C129" s="2"/>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:3">
       <c r="C130" s="2"/>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:3">
       <c r="C131" s="2"/>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:3">
       <c r="C132" s="2"/>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:3">
       <c r="C133" s="2"/>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:3">
       <c r="C134" s="2"/>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:3">
       <c r="C135" s="2"/>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:3">
       <c r="C136" s="2"/>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:3">
       <c r="C137" s="2"/>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:3">
       <c r="C138" s="2"/>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:3">
       <c r="C139" s="2"/>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:3">
       <c r="C140" s="2"/>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:3">
       <c r="C141" s="2"/>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:3">
       <c r="C142" s="2"/>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:3">
       <c r="C143" s="2"/>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:3">
       <c r="C144" s="2"/>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:3">
       <c r="C145" s="2"/>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:3">
       <c r="C146" s="2"/>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:3">
       <c r="C147" s="2"/>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:3">
       <c r="C148" s="2"/>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:3">
       <c r="C149" s="2"/>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:3">
       <c r="C150" s="2"/>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:3">
       <c r="C151" s="2"/>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:3">
       <c r="C152" s="2"/>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:3">
       <c r="C153" s="2"/>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:3">
       <c r="C154" s="2"/>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:3">
       <c r="C155" s="2"/>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:3">
       <c r="C156" s="2"/>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:3">
       <c r="C157" s="2"/>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:3">
       <c r="C158" s="2"/>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:3">
       <c r="C159" s="2"/>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:3">
       <c r="C160" s="2"/>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:3">
       <c r="C161" s="2"/>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:3">
       <c r="C162" s="2"/>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:3">
       <c r="C163" s="2"/>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:3">
       <c r="C164" s="2"/>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:3">
       <c r="C165" s="2"/>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:3">
       <c r="C166" s="2"/>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:3">
       <c r="C167" s="2"/>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:3">
       <c r="C168" s="2"/>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:3">
       <c r="C169" s="2"/>
     </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:3">
       <c r="C170" s="2"/>
     </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:3">
       <c r="C171" s="2"/>
     </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:3">
       <c r="C172" s="2"/>
     </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:3">
       <c r="C173" s="2"/>
     </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:3">
       <c r="C174" s="2"/>
     </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:3">
       <c r="C175" s="2"/>
     </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:3">
       <c r="C176" s="2"/>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:3">
       <c r="C177" s="2"/>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:3">
       <c r="C178" s="2"/>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:3">
       <c r="C179" s="2"/>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:3">
       <c r="C180" s="2"/>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:3">
       <c r="C181" s="2"/>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:3">
       <c r="C182" s="2"/>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:3">
       <c r="C183" s="2"/>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:3">
       <c r="C184" s="2"/>
     </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:3">
       <c r="C185" s="2"/>
     </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:3">
       <c r="C186" s="2"/>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:3">
       <c r="C187" s="2"/>
     </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:3">
       <c r="C188" s="2"/>
     </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:3">
       <c r="C189" s="2"/>
     </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:3">
       <c r="C190" s="2"/>
     </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:3">
       <c r="C191" s="2"/>
     </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:3">
       <c r="C192" s="2"/>
     </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:3">
       <c r="C193" s="2"/>
     </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:3">
       <c r="C194" s="2"/>
     </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:3">
       <c r="C195" s="2"/>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:3">
       <c r="C196" s="2"/>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:3">
       <c r="C197" s="2"/>
     </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:3">
       <c r="C198" s="2"/>
     </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:3">
       <c r="C199" s="2"/>
     </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:3">
       <c r="C200" s="2"/>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:3">
       <c r="C201" s="2"/>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:3">
       <c r="C202" s="2"/>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:3">
       <c r="C203" s="2"/>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:3">
       <c r="C204" s="2"/>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:3">
       <c r="C205" s="2"/>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:3">
       <c r="C206" s="2"/>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:3">
       <c r="C207" s="2"/>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:3">
       <c r="C208" s="2"/>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="3:3">
       <c r="C209" s="2"/>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="3:3">
       <c r="C210" s="2"/>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="3:3">
       <c r="C211" s="2"/>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="3:3">
       <c r="C212" s="2"/>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="3:3">
       <c r="C213" s="2"/>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="3:3">
       <c r="C214" s="2"/>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="3:3">
       <c r="C215" s="2"/>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="3:3">
       <c r="C216" s="2"/>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="3:3">
       <c r="C217" s="2"/>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="3:3">
       <c r="C218" s="2"/>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="3:3">
       <c r="C219" s="2"/>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="3:3">
       <c r="C220" s="2"/>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="3:3">
       <c r="C221" s="2"/>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="3:3">
       <c r="C222" s="2"/>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="3:3">
       <c r="C223" s="2"/>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="3:3">
       <c r="C224" s="2"/>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="3:3">
       <c r="C225" s="2"/>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="3:3">
       <c r="C226" s="2"/>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="3:3">
       <c r="C227" s="2"/>
     </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="3:3">
       <c r="C228" s="2"/>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="3:3">
       <c r="C229" s="2"/>
     </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="3:3">
       <c r="C230" s="2"/>
     </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="3:3">
       <c r="C231" s="2"/>
     </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="3:3">
       <c r="C232" s="2"/>
     </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="3:3">
       <c r="C233" s="2"/>
     </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="3:3">
       <c r="C234" s="2"/>
     </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="3:3">
       <c r="C235" s="2"/>
     </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="3:3">
       <c r="C236" s="2"/>
     </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="3:3">
       <c r="C237" s="2"/>
     </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="3:3">
       <c r="C238" s="2"/>
     </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="3:3">
       <c r="C239" s="2"/>
     </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="3:3">
       <c r="C240" s="2"/>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="3:3">
       <c r="C241" s="2"/>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="3:3">
       <c r="C242" s="2"/>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="3:3">
       <c r="C243" s="2"/>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="3:3">
       <c r="C244" s="2"/>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="3:3">
       <c r="C245" s="2"/>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="3:3">
       <c r="C246" s="2"/>
     </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="3:3">
       <c r="C247" s="2"/>
     </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="3:3">
       <c r="C248" s="2"/>
     </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="3:3">
       <c r="C249" s="2"/>
     </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="3:3">
       <c r="C250" s="2"/>
     </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="3:3">
       <c r="C251" s="2"/>
     </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="3:3">
       <c r="C252" s="2"/>
     </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="3:3">
       <c r="C253" s="2"/>
     </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="3:3">
       <c r="C254" s="2"/>
     </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="3:3">
       <c r="C255" s="2"/>
     </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="3:3">
       <c r="C256" s="2"/>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:3">
       <c r="C257" s="2"/>
     </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:3">
       <c r="C258" s="2"/>
     </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:3">
       <c r="C259" s="2"/>
     </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:3">
       <c r="C260" s="2"/>
     </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:3">
       <c r="C261" s="2"/>
     </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:3">
       <c r="C262" s="2"/>
     </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:3">
       <c r="C263" s="2"/>
     </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:3">
       <c r="C264" s="2"/>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:3">
       <c r="C265" s="2"/>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:3">
       <c r="C266" s="2"/>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:3">
       <c r="C267" s="2"/>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:3">
       <c r="C268" s="2"/>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:3">
       <c r="C269" s="2"/>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:3">
       <c r="C270" s="2"/>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:3">
       <c r="C271" s="2"/>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:3">
       <c r="C272" s="2"/>
     </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:3">
       <c r="C273" s="2"/>
     </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:3">
       <c r="C274" s="2"/>
     </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:3">
       <c r="C275" s="2"/>
     </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:3">
       <c r="C276" s="2"/>
     </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:3">
       <c r="C277" s="2"/>
     </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:3">
       <c r="C278" s="2"/>
     </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:3">
       <c r="C279" s="2"/>
     </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:3">
       <c r="C280" s="2"/>
     </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:3">
       <c r="C281" s="2"/>
     </row>
-    <row r="282" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:3">
       <c r="C282" s="2"/>
     </row>
-    <row r="283" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:3">
       <c r="C283" s="2"/>
     </row>
-    <row r="284" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:3">
       <c r="C284" s="2"/>
     </row>
-    <row r="285" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:3">
       <c r="C285" s="2"/>
     </row>
-    <row r="286" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:3">
       <c r="C286" s="2"/>
     </row>
-    <row r="287" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:3">
       <c r="C287" s="2"/>
     </row>
-    <row r="288" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:3">
       <c r="C288" s="2"/>
     </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:3">
       <c r="C289" s="2"/>
     </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:3">
       <c r="C290" s="2"/>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:3">
       <c r="C291" s="2"/>
     </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:3">
       <c r="C292" s="2"/>
     </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:3">
       <c r="C293" s="2"/>
     </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:3">
       <c r="C294" s="2"/>
     </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:3">
       <c r="C295" s="2"/>
     </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:3">
       <c r="C296" s="2"/>
     </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:3">
       <c r="C297" s="2"/>
     </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:3">
       <c r="C298" s="2"/>
     </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:3">
       <c r="C299" s="2"/>
     </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:3">
       <c r="C300" s="2"/>
     </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:3">
       <c r="C301" s="2"/>
     </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:3">
       <c r="C302" s="2"/>
     </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:3">
       <c r="C303" s="2"/>
     </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:3">
       <c r="C304" s="2"/>
     </row>
-    <row r="305" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:3">
       <c r="C305" s="2"/>
     </row>
-    <row r="306" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:3">
       <c r="C306" s="2"/>
     </row>
-    <row r="307" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:3">
       <c r="C307" s="2"/>
     </row>
-    <row r="308" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:3">
       <c r="C308" s="2"/>
     </row>
-    <row r="309" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:3">
       <c r="C309" s="2"/>
     </row>
-    <row r="310" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:3">
       <c r="C310" s="2"/>
     </row>
-    <row r="311" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:3">
       <c r="C311" s="2"/>
     </row>
-    <row r="312" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:3">
       <c r="C312" s="2"/>
     </row>
-    <row r="313" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:3">
       <c r="C313" s="2"/>
     </row>
-    <row r="314" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:3">
       <c r="C314" s="2"/>
     </row>
-    <row r="315" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:3">
       <c r="C315" s="2"/>
     </row>
-    <row r="316" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:3">
       <c r="C316" s="2"/>
     </row>
-    <row r="317" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:3">
       <c r="C317" s="2"/>
     </row>
-    <row r="318" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:3">
       <c r="C318" s="2"/>
     </row>
-    <row r="319" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:3">
       <c r="C319" s="2"/>
     </row>
-    <row r="320" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:3">
       <c r="C320" s="2"/>
     </row>
-    <row r="321" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:3">
       <c r="C321" s="2"/>
     </row>
-    <row r="322" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:3">
       <c r="C322" s="2"/>
     </row>
-    <row r="323" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:3">
       <c r="C323" s="2"/>
     </row>
-    <row r="324" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="3:3">
       <c r="C324" s="2"/>
     </row>
-    <row r="325" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="3:3">
       <c r="C325" s="2"/>
     </row>
-    <row r="326" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="3:3">
       <c r="C326" s="2"/>
     </row>
-    <row r="327" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="3:3">
       <c r="C327" s="2"/>
     </row>
-    <row r="328" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="3:3">
       <c r="C328" s="2"/>
     </row>
-    <row r="329" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="3:3">
       <c r="C329" s="2"/>
     </row>
-    <row r="330" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="3:3">
       <c r="C330" s="2"/>
     </row>
-    <row r="331" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="3:3">
       <c r="C331" s="2"/>
     </row>
-    <row r="332" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="3:3">
       <c r="C332" s="2"/>
     </row>
-    <row r="333" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="3:3">
       <c r="C333" s="2"/>
     </row>
-    <row r="334" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="3:3">
       <c r="C334" s="2"/>
     </row>
-    <row r="335" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="3:3">
       <c r="C335" s="2"/>
     </row>
-    <row r="336" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="3:3">
       <c r="C336" s="2"/>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="3:3">
       <c r="C337" s="2"/>
     </row>
-    <row r="338" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="3:3">
       <c r="C338" s="2"/>
     </row>
-    <row r="339" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="3:3">
       <c r="C339" s="2"/>
     </row>
-    <row r="340" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="3:3">
       <c r="C340" s="2"/>
     </row>
-    <row r="341" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="3:3">
       <c r="C341" s="2"/>
     </row>
-    <row r="342" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="3:3">
       <c r="C342" s="2"/>
     </row>
-    <row r="343" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="3:3">
       <c r="C343" s="2"/>
     </row>
-    <row r="344" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="3:3">
       <c r="C344" s="2"/>
     </row>
-    <row r="345" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="3:3">
       <c r="C345" s="2"/>
     </row>
-    <row r="346" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="3:3">
       <c r="C346" s="2"/>
     </row>
-    <row r="347" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="3:3">
       <c r="C347" s="2"/>
     </row>
-    <row r="348" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="3:3">
       <c r="C348" s="2"/>
     </row>
-    <row r="349" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="3:3">
       <c r="C349" s="2"/>
     </row>
-    <row r="350" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="3:3">
       <c r="C350" s="2"/>
     </row>
-    <row r="351" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="3:3">
       <c r="C351" s="2"/>
     </row>
-    <row r="352" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="3:3">
       <c r="C352" s="2"/>
     </row>
-    <row r="353" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="3:3">
       <c r="C353" s="2"/>
     </row>
-    <row r="354" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="3:3">
       <c r="C354" s="2"/>
     </row>
-    <row r="355" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="3:3">
       <c r="C355" s="2"/>
     </row>
-    <row r="356" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="3:3">
       <c r="C356" s="2"/>
     </row>
-    <row r="357" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="3:3">
       <c r="C357" s="2"/>
     </row>
-    <row r="358" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="3:3">
       <c r="C358" s="2"/>
     </row>
-    <row r="359" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="3:3">
       <c r="C359" s="2"/>
     </row>
-    <row r="360" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="3:3">
       <c r="C360" s="2"/>
     </row>
-    <row r="361" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="3:3">
       <c r="C361" s="2"/>
     </row>
-    <row r="362" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="3:3">
       <c r="C362" s="2"/>
     </row>
-    <row r="363" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="3:3">
       <c r="C363" s="2"/>
     </row>
-    <row r="364" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="3:3">
       <c r="C364" s="2"/>
     </row>
-    <row r="365" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="3:3">
       <c r="C365" s="2"/>
     </row>
-    <row r="366" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="3:3">
       <c r="C366" s="2"/>
     </row>
-    <row r="367" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="3:3">
       <c r="C367" s="2"/>
     </row>
-    <row r="368" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="3:3">
       <c r="C368" s="2"/>
     </row>
-    <row r="369" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="3:3">
       <c r="C369" s="2"/>
     </row>
-    <row r="370" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="3:3">
       <c r="C370" s="2"/>
     </row>
-    <row r="371" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="3:3">
       <c r="C371" s="2"/>
     </row>
-    <row r="372" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="3:3">
       <c r="C372" s="2"/>
     </row>
-    <row r="373" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="3:3">
       <c r="C373" s="2"/>
     </row>
-    <row r="374" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="3:3">
       <c r="C374" s="2"/>
     </row>
-    <row r="375" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="3:3">
       <c r="C375" s="2"/>
     </row>
-    <row r="376" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="3:3">
       <c r="C376" s="2"/>
     </row>
-    <row r="377" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="3:3">
       <c r="C377" s="2"/>
     </row>
-    <row r="378" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="3:3">
       <c r="C378" s="2"/>
     </row>
-    <row r="379" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="3:3">
       <c r="C379" s="2"/>
     </row>
-    <row r="380" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="3:3">
       <c r="C380" s="2"/>
     </row>
-    <row r="381" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="3:3">
       <c r="C381" s="2"/>
     </row>
-    <row r="382" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="3:3">
       <c r="C382" s="2"/>
     </row>
-    <row r="383" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="3:3">
       <c r="C383" s="2"/>
     </row>
-    <row r="384" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="3:3">
       <c r="C384" s="2"/>
     </row>
-    <row r="385" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="3:3">
       <c r="C385" s="2"/>
     </row>
-    <row r="386" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="3:3">
       <c r="C386" s="2"/>
     </row>
-    <row r="387" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="3:3">
       <c r="C387" s="2"/>
     </row>
-    <row r="388" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="3:3">
       <c r="C388" s="2"/>
     </row>
-    <row r="389" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="3:3">
       <c r="C389" s="2"/>
     </row>
-    <row r="390" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="3:3">
       <c r="C390" s="2"/>
     </row>
-    <row r="391" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="3:3">
       <c r="C391" s="2"/>
     </row>
-    <row r="392" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="3:3">
       <c r="C392" s="2"/>
     </row>
-    <row r="393" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="3:3">
       <c r="C393" s="2"/>
     </row>
-    <row r="394" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="3:3">
       <c r="C394" s="2"/>
     </row>
-    <row r="395" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="3:3">
       <c r="C395" s="2"/>
     </row>
-    <row r="396" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="3:3">
       <c r="C396" s="2"/>
     </row>
-    <row r="397" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="3:3">
       <c r="C397" s="2"/>
     </row>
-    <row r="398" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="3:3">
       <c r="C398" s="2"/>
     </row>
-    <row r="399" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="3:3">
       <c r="C399" s="2"/>
     </row>
-    <row r="400" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="3:3">
       <c r="C400" s="2"/>
     </row>
-    <row r="401" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="3:3">
       <c r="C401" s="2"/>
     </row>
-    <row r="402" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="3:3">
       <c r="C402" s="2"/>
     </row>
-    <row r="403" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="3:3">
       <c r="C403" s="2"/>
     </row>
-    <row r="404" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="3:3">
       <c r="C404" s="2"/>
     </row>
-    <row r="405" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="3:3">
       <c r="C405" s="2"/>
     </row>
-    <row r="406" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="3:3">
       <c r="C406" s="2"/>
     </row>
-    <row r="407" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="3:3">
       <c r="C407" s="2"/>
     </row>
-    <row r="408" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="3:3">
       <c r="C408" s="2"/>
     </row>
-    <row r="409" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="3:3">
       <c r="C409" s="2"/>
     </row>
-    <row r="410" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="3:3">
       <c r="C410" s="2"/>
     </row>
-    <row r="411" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="3:3">
       <c r="C411" s="2"/>
     </row>
-    <row r="412" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="3:3">
       <c r="C412" s="2"/>
     </row>
-    <row r="413" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="3:3">
       <c r="C413" s="2"/>
     </row>
-    <row r="414" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="3:3">
       <c r="C414" s="2"/>
     </row>
-    <row r="415" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="3:3">
       <c r="C415" s="2"/>
     </row>
-    <row r="416" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="3:3">
       <c r="C416" s="2"/>
     </row>
-    <row r="417" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="3:3">
       <c r="C417" s="2"/>
     </row>
-    <row r="418" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="3:3">
       <c r="C418" s="2"/>
     </row>
-    <row r="419" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="3:3">
       <c r="C419" s="2"/>
     </row>
-    <row r="420" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="3:3">
       <c r="C420" s="2"/>
     </row>
-    <row r="421" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="3:3">
       <c r="C421" s="2"/>
     </row>
-    <row r="422" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="3:3">
       <c r="C422" s="2"/>
     </row>
-    <row r="423" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="3:3">
       <c r="C423" s="2"/>
     </row>
-    <row r="424" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="3:3">
       <c r="C424" s="2"/>
     </row>
-    <row r="425" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="3:3">
       <c r="C425" s="2"/>
     </row>
-    <row r="426" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="3:3">
       <c r="C426" s="2"/>
     </row>
-    <row r="427" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="3:3">
       <c r="C427" s="2"/>
     </row>
-    <row r="428" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="3:3">
       <c r="C428" s="2"/>
     </row>
-    <row r="429" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="3:3">
       <c r="C429" s="2"/>
     </row>
-    <row r="430" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="3:3">
       <c r="C430" s="2"/>
     </row>
-    <row r="431" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="3:3">
       <c r="C431" s="2"/>
     </row>
-    <row r="432" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="3:3">
       <c r="C432" s="2"/>
     </row>
-    <row r="433" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="3:3">
       <c r="C433" s="2"/>
     </row>
-    <row r="434" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="3:3">
       <c r="C434" s="2"/>
     </row>
-    <row r="435" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="3:3">
       <c r="C435" s="2"/>
     </row>
-    <row r="436" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="3:3">
       <c r="C436" s="2"/>
     </row>
-    <row r="437" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="3:3">
       <c r="C437" s="2"/>
     </row>
-    <row r="438" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="3:3">
       <c r="C438" s="2"/>
     </row>
-    <row r="439" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="3:3">
       <c r="C439" s="2"/>
     </row>
-    <row r="440" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="3:3">
       <c r="C440" s="2"/>
     </row>
-    <row r="441" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="3:3">
       <c r="C441" s="2"/>
     </row>
-    <row r="442" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="3:3">
       <c r="C442" s="2"/>
     </row>
-    <row r="443" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="3:3">
       <c r="C443" s="2"/>
     </row>
-    <row r="444" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="3:3">
       <c r="C444" s="2"/>
     </row>
-    <row r="445" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="3:3">
       <c r="C445" s="2"/>
     </row>
-    <row r="446" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="3:3">
       <c r="C446" s="2"/>
     </row>
-    <row r="447" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="3:3">
       <c r="C447" s="2"/>
     </row>
-    <row r="448" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="3:3">
       <c r="C448" s="2"/>
     </row>
-    <row r="449" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="3:3">
       <c r="C449" s="2"/>
     </row>
-    <row r="450" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="3:3">
       <c r="C450" s="2"/>
     </row>
-    <row r="451" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="3:3">
       <c r="C451" s="2"/>
     </row>
-    <row r="452" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="3:3">
       <c r="C452" s="2"/>
     </row>
-    <row r="453" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="3:3">
       <c r="C453" s="2"/>
     </row>
-    <row r="454" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="3:3">
       <c r="C454" s="2"/>
     </row>
-    <row r="455" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="3:3">
       <c r="C455" s="2"/>
     </row>
-    <row r="456" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="3:3">
       <c r="C456" s="2"/>
     </row>
-    <row r="457" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="3:3">
       <c r="C457" s="2"/>
     </row>
-    <row r="458" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="3:3">
       <c r="C458" s="2"/>
     </row>
-    <row r="459" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="3:3">
       <c r="C459" s="2"/>
     </row>
-    <row r="460" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="3:3">
       <c r="C460" s="2"/>
     </row>
-    <row r="461" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="3:3">
       <c r="C461" s="2"/>
     </row>
-    <row r="462" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="3:3">
       <c r="C462" s="2"/>
     </row>
-    <row r="463" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="3:3">
       <c r="C463" s="2"/>
     </row>
-    <row r="464" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="3:3">
       <c r="C464" s="2"/>
     </row>
-    <row r="465" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="3:3">
       <c r="C465" s="2"/>
     </row>
-    <row r="466" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="3:3">
       <c r="C466" s="2"/>
     </row>
-    <row r="467" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="3:3">
       <c r="C467" s="2"/>
     </row>
-    <row r="468" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="3:3">
       <c r="C468" s="2"/>
     </row>
-    <row r="469" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="3:3">
       <c r="C469" s="2"/>
     </row>
-    <row r="470" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="3:3">
       <c r="C470" s="2"/>
     </row>
-    <row r="471" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="3:3">
       <c r="C471" s="2"/>
     </row>
-    <row r="472" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="3:3">
       <c r="C472" s="2"/>
     </row>
-    <row r="473" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="3:3">
       <c r="C473" s="2"/>
     </row>
-    <row r="474" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="3:3">
       <c r="C474" s="2"/>
     </row>
-    <row r="475" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="3:3">
       <c r="C475" s="2"/>
     </row>
-    <row r="476" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="3:3">
       <c r="C476" s="2"/>
     </row>
-    <row r="477" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="3:3">
       <c r="C477" s="2"/>
     </row>
-    <row r="478" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="3:3">
       <c r="C478" s="2"/>
     </row>
-    <row r="479" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="3:3">
       <c r="C479" s="2"/>
     </row>
-    <row r="480" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="3:3">
       <c r="C480" s="2"/>
     </row>
-    <row r="481" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="3:3">
       <c r="C481" s="2"/>
     </row>
-    <row r="482" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="3:3">
       <c r="C482" s="2"/>
     </row>
-    <row r="483" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="3:3">
       <c r="C483" s="2"/>
     </row>
-    <row r="484" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="3:3">
       <c r="C484" s="2"/>
     </row>
-    <row r="485" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="3:3">
       <c r="C485" s="2"/>
     </row>
-    <row r="486" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="3:3">
       <c r="C486" s="2"/>
     </row>
-    <row r="487" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="3:3">
       <c r="C487" s="2"/>
     </row>
-    <row r="488" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="3:3">
       <c r="C488" s="2"/>
     </row>
-    <row r="489" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="3:3">
       <c r="C489" s="2"/>
     </row>
-    <row r="490" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="3:3">
       <c r="C490" s="2"/>
     </row>
-    <row r="491" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="3:3">
       <c r="C491" s="2"/>
     </row>
-    <row r="492" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="3:3">
       <c r="C492" s="2"/>
     </row>
-    <row r="493" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="3:3">
       <c r="C493" s="2"/>
     </row>
-    <row r="494" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="3:3">
       <c r="C494" s="2"/>
     </row>
-    <row r="495" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="3:3">
       <c r="C495" s="2"/>
     </row>
-    <row r="496" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="3:3">
       <c r="C496" s="2"/>
     </row>
-    <row r="497" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="3:3">
       <c r="C497" s="2"/>
     </row>
-    <row r="498" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="3:3">
       <c r="C498" s="2"/>
     </row>
-    <row r="499" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="3:3">
       <c r="C499" s="2"/>
     </row>
-    <row r="500" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="3:3">
       <c r="C500" s="2"/>
     </row>
-    <row r="501" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="3:3">
       <c r="C501" s="2"/>
     </row>
-    <row r="502" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="3:3">
       <c r="C502" s="2"/>
     </row>
-    <row r="503" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="3:3">
       <c r="C503" s="2"/>
     </row>
-    <row r="504" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="3:3">
       <c r="C504" s="2"/>
     </row>
-    <row r="505" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="3:3">
       <c r="C505" s="2"/>
     </row>
-    <row r="506" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="3:3">
       <c r="C506" s="2"/>
     </row>
-    <row r="507" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="3:3">
       <c r="C507" s="2"/>
     </row>
-    <row r="508" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="3:3">
       <c r="C508" s="2"/>
     </row>
-    <row r="509" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="3:3">
       <c r="C509" s="2"/>
     </row>
-    <row r="510" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="3:3">
       <c r="C510" s="2"/>
     </row>
-    <row r="511" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="3:3">
       <c r="C511" s="2"/>
     </row>
-    <row r="512" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="3:3">
       <c r="C512" s="2"/>
     </row>
-    <row r="513" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="3:3">
       <c r="C513" s="2"/>
     </row>
-    <row r="514" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="3:3">
       <c r="C514" s="2"/>
     </row>
-    <row r="515" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="3:3">
       <c r="C515" s="2"/>
     </row>
-    <row r="516" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="3:3">
       <c r="C516" s="2"/>
     </row>
-    <row r="517" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="3:3">
       <c r="C517" s="2"/>
     </row>
-    <row r="518" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="3:3">
       <c r="C518" s="2"/>
     </row>
-    <row r="519" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="3:3">
       <c r="C519" s="2"/>
     </row>
-    <row r="520" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="3:3">
       <c r="C520" s="2"/>
     </row>
-    <row r="521" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="3:3">
       <c r="C521" s="2"/>
     </row>
-    <row r="522" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="3:3">
       <c r="C522" s="2"/>
     </row>
-    <row r="523" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="3:3">
       <c r="C523" s="2"/>
     </row>
-    <row r="524" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="3:3">
       <c r="C524" s="2"/>
     </row>
-    <row r="525" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="3:3">
       <c r="C525" s="2"/>
     </row>
-    <row r="526" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="3:3">
       <c r="C526" s="2"/>
     </row>
-    <row r="527" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="3:3">
       <c r="C527" s="2"/>
     </row>
-    <row r="528" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="3:3">
       <c r="C528" s="2"/>
     </row>
-    <row r="529" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="3:3">
       <c r="C529" s="2"/>
     </row>
-    <row r="530" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="3:3">
       <c r="C530" s="2"/>
     </row>
-    <row r="531" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="531" spans="3:3">
       <c r="C531" s="2"/>
     </row>
-    <row r="532" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="3:3">
       <c r="C532" s="2"/>
     </row>
-    <row r="533" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="3:3">
       <c r="C533" s="2"/>
     </row>
-    <row r="534" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="3:3">
       <c r="C534" s="2"/>
     </row>
-    <row r="535" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="3:3">
       <c r="C535" s="2"/>
     </row>
-    <row r="536" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="3:3">
       <c r="C536" s="2"/>
     </row>
-    <row r="537" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="3:3">
       <c r="C537" s="2"/>
     </row>
-    <row r="538" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="3:3">
       <c r="C538" s="2"/>
     </row>
-    <row r="539" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="3:3">
       <c r="C539" s="2"/>
     </row>
-    <row r="540" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="3:3">
       <c r="C540" s="2"/>
     </row>
-    <row r="541" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="3:3">
       <c r="C541" s="2"/>
     </row>
-    <row r="542" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="3:3">
       <c r="C542" s="2"/>
     </row>
-    <row r="543" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="3:3">
       <c r="C543" s="2"/>
     </row>
-    <row r="544" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="3:3">
       <c r="C544" s="2"/>
     </row>
-    <row r="545" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="3:3">
       <c r="C545" s="2"/>
     </row>
-    <row r="546" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="3:3">
       <c r="C546" s="2"/>
     </row>
-    <row r="547" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="3:3">
       <c r="C547" s="2"/>
     </row>
-    <row r="548" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="3:3">
       <c r="C548" s="2"/>
     </row>
-    <row r="549" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="3:3">
       <c r="C549" s="2"/>
     </row>
-    <row r="550" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="3:3">
       <c r="C550" s="2"/>
     </row>
-    <row r="551" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="3:3">
       <c r="C551" s="2"/>
     </row>
-    <row r="552" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="3:3">
       <c r="C552" s="2"/>
     </row>
-    <row r="553" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="3:3">
       <c r="C553" s="2"/>
     </row>
-    <row r="554" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="3:3">
       <c r="C554" s="2"/>
     </row>
-    <row r="555" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="3:3">
       <c r="C555" s="2"/>
     </row>
-    <row r="556" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="3:3">
       <c r="C556" s="2"/>
     </row>
-    <row r="557" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="3:3">
       <c r="C557" s="2"/>
     </row>
-    <row r="558" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="3:3">
       <c r="C558" s="2"/>
     </row>
-    <row r="559" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="3:3">
       <c r="C559" s="2"/>
     </row>
-    <row r="560" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="3:3">
       <c r="C560" s="2"/>
     </row>
-    <row r="561" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="3:3">
       <c r="C561" s="2"/>
     </row>
-    <row r="562" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="3:3">
       <c r="C562" s="2"/>
     </row>
-    <row r="563" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="3:3">
       <c r="C563" s="2"/>
     </row>
-    <row r="564" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="564" spans="3:3">
       <c r="C564" s="2"/>
     </row>
-    <row r="565" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="565" spans="3:3">
       <c r="C565" s="2"/>
     </row>
-    <row r="566" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="566" spans="3:3">
       <c r="C566" s="2"/>
     </row>
-    <row r="567" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="567" spans="3:3">
       <c r="C567" s="2"/>
     </row>
-    <row r="568" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="568" spans="3:3">
       <c r="C568" s="2"/>
     </row>
-    <row r="569" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="569" spans="3:3">
       <c r="C569" s="2"/>
     </row>
-    <row r="570" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="570" spans="3:3">
       <c r="C570" s="2"/>
     </row>
-    <row r="571" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="571" spans="3:3">
       <c r="C571" s="2"/>
     </row>
-    <row r="572" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="572" spans="3:3">
       <c r="C572" s="2"/>
     </row>
-    <row r="573" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="573" spans="3:3">
       <c r="C573" s="2"/>
     </row>
-    <row r="574" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="574" spans="3:3">
       <c r="C574" s="2"/>
     </row>
-    <row r="575" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="575" spans="3:3">
       <c r="C575" s="2"/>
     </row>
-    <row r="576" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="576" spans="3:3">
       <c r="C576" s="2"/>
     </row>
-    <row r="577" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="577" spans="3:3">
       <c r="C577" s="2"/>
     </row>
-    <row r="578" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="578" spans="3:3">
       <c r="C578" s="2"/>
     </row>
-    <row r="579" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="579" spans="3:3">
       <c r="C579" s="2"/>
     </row>
-    <row r="580" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="580" spans="3:3">
       <c r="C580" s="2"/>
     </row>
-    <row r="581" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="581" spans="3:3">
       <c r="C581" s="2"/>
     </row>
-    <row r="582" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="582" spans="3:3">
       <c r="C582" s="2"/>
     </row>
-    <row r="583" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="583" spans="3:3">
       <c r="C583" s="2"/>
     </row>
-    <row r="584" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="584" spans="3:3">
       <c r="C584" s="2"/>
     </row>
-    <row r="585" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="585" spans="3:3">
       <c r="C585" s="2"/>
     </row>
-    <row r="586" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="586" spans="3:3">
       <c r="C586" s="2"/>
     </row>
-    <row r="587" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="587" spans="3:3">
       <c r="C587" s="2"/>
     </row>
-    <row r="588" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="588" spans="3:3">
       <c r="C588" s="2"/>
     </row>
-    <row r="589" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="589" spans="3:3">
       <c r="C589" s="2"/>
     </row>
-    <row r="590" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="590" spans="3:3">
       <c r="C590" s="2"/>
     </row>
-    <row r="591" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="591" spans="3:3">
       <c r="C591" s="2"/>
     </row>
-    <row r="592" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="592" spans="3:3">
       <c r="C592" s="2"/>
     </row>
-    <row r="593" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="593" spans="3:3">
       <c r="C593" s="2"/>
     </row>
-    <row r="594" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="594" spans="3:3">
       <c r="C594" s="2"/>
     </row>
-    <row r="595" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="595" spans="3:3">
       <c r="C595" s="2"/>
     </row>
-    <row r="596" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="596" spans="3:3">
       <c r="C596" s="2"/>
     </row>
-    <row r="597" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="597" spans="3:3">
       <c r="C597" s="2"/>
     </row>
-    <row r="598" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="598" spans="3:3">
       <c r="C598" s="2"/>
     </row>
-    <row r="599" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="599" spans="3:3">
       <c r="C599" s="2"/>
     </row>
-    <row r="600" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="600" spans="3:3">
       <c r="C600" s="2"/>
     </row>
-    <row r="601" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="601" spans="3:3">
       <c r="C601" s="2"/>
     </row>
-    <row r="602" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="602" spans="3:3">
       <c r="C602" s="2"/>
     </row>
-    <row r="603" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="603" spans="3:3">
       <c r="C603" s="2"/>
     </row>
-    <row r="604" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="604" spans="3:3">
       <c r="C604" s="2"/>
     </row>
-    <row r="605" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="605" spans="3:3">
       <c r="C605" s="2"/>
     </row>
-    <row r="606" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="606" spans="3:3">
       <c r="C606" s="2"/>
     </row>
-    <row r="607" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="607" spans="3:3">
       <c r="C607" s="2"/>
     </row>
-    <row r="608" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="608" spans="3:3">
       <c r="C608" s="2"/>
     </row>
-    <row r="609" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="609" spans="3:3">
       <c r="C609" s="2"/>
     </row>
-    <row r="610" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="610" spans="3:3">
       <c r="C610" s="2"/>
     </row>
-    <row r="611" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="611" spans="3:3">
       <c r="C611" s="2"/>
     </row>
-    <row r="612" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="612" spans="3:3">
       <c r="C612" s="2"/>
     </row>
-    <row r="613" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="613" spans="3:3">
       <c r="C613" s="2"/>
     </row>
-    <row r="614" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="614" spans="3:3">
       <c r="C614" s="2"/>
     </row>
-    <row r="615" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="615" spans="3:3">
       <c r="C615" s="2"/>
     </row>
-    <row r="616" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="616" spans="3:3">
       <c r="C616" s="2"/>
     </row>
-    <row r="617" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="617" spans="3:3">
       <c r="C617" s="2"/>
     </row>
-    <row r="618" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="618" spans="3:3">
       <c r="C618" s="2"/>
     </row>
-    <row r="619" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="619" spans="3:3">
       <c r="C619" s="2"/>
     </row>
-    <row r="620" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="620" spans="3:3">
       <c r="C620" s="2"/>
     </row>
-    <row r="621" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="621" spans="3:3">
       <c r="C621" s="2"/>
     </row>
-    <row r="622" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="622" spans="3:3">
       <c r="C622" s="2"/>
     </row>
-    <row r="623" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="623" spans="3:3">
       <c r="C623" s="2"/>
     </row>
-    <row r="624" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="624" spans="3:3">
       <c r="C624" s="2"/>
     </row>
-    <row r="625" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="3:3">
       <c r="C625" s="2"/>
     </row>
-    <row r="626" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="3:3">
       <c r="C626" s="2"/>
     </row>
-    <row r="627" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="3:3">
       <c r="C627" s="2"/>
     </row>
-    <row r="628" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="628" spans="3:3">
       <c r="C628" s="2"/>
     </row>
-    <row r="629" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="3:3">
       <c r="C629" s="2"/>
     </row>
-    <row r="630" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="3:3">
       <c r="C630" s="2"/>
     </row>
-    <row r="631" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="3:3">
       <c r="C631" s="2"/>
     </row>
-    <row r="632" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="632" spans="3:3">
       <c r="C632" s="2"/>
     </row>
-    <row r="633" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="3:3">
       <c r="C633" s="2"/>
     </row>
-    <row r="634" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="634" spans="3:3">
       <c r="C634" s="2"/>
     </row>
-    <row r="635" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="635" spans="3:3">
       <c r="C635" s="2"/>
     </row>
-    <row r="636" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="636" spans="3:3">
       <c r="C636" s="2"/>
     </row>
-    <row r="637" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="637" spans="3:3">
       <c r="C637" s="2"/>
     </row>
-    <row r="638" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="638" spans="3:3">
       <c r="C638" s="2"/>
     </row>
-    <row r="639" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="639" spans="3:3">
       <c r="C639" s="2"/>
     </row>
-    <row r="640" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="640" spans="3:3">
       <c r="C640" s="2"/>
     </row>
-    <row r="641" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="641" spans="3:3">
       <c r="C641" s="2"/>
     </row>
-    <row r="642" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="642" spans="3:3">
       <c r="C642" s="2"/>
     </row>
-    <row r="643" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="643" spans="3:3">
       <c r="C643" s="2"/>
     </row>
-    <row r="644" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="644" spans="3:3">
       <c r="C644" s="2"/>
     </row>
-    <row r="645" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="645" spans="3:3">
       <c r="C645" s="2"/>
     </row>
-    <row r="646" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="646" spans="3:3">
       <c r="C646" s="2"/>
     </row>
-    <row r="647" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="647" spans="3:3">
       <c r="C647" s="2"/>
     </row>
-    <row r="648" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="648" spans="3:3">
       <c r="C648" s="2"/>
     </row>
-    <row r="649" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="649" spans="3:3">
       <c r="C649" s="2"/>
     </row>
-    <row r="650" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="650" spans="3:3">
       <c r="C650" s="2"/>
     </row>
-    <row r="651" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="651" spans="3:3">
       <c r="C651" s="2"/>
     </row>
-    <row r="652" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="652" spans="3:3">
       <c r="C652" s="2"/>
     </row>
-    <row r="653" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="653" spans="3:3">
       <c r="C653" s="2"/>
     </row>
-    <row r="654" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="654" spans="3:3">
       <c r="C654" s="2"/>
     </row>
-    <row r="655" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="655" spans="3:3">
       <c r="C655" s="2"/>
     </row>
-    <row r="656" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="656" spans="3:3">
       <c r="C656" s="2"/>
     </row>
-    <row r="657" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="657" spans="3:3">
       <c r="C657" s="2"/>
     </row>
-    <row r="658" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="658" spans="3:3">
       <c r="C658" s="2"/>
     </row>
-    <row r="659" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="659" spans="3:3">
       <c r="C659" s="2"/>
     </row>
-    <row r="660" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="660" spans="3:3">
       <c r="C660" s="2"/>
     </row>
-    <row r="661" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="661" spans="3:3">
       <c r="C661" s="2"/>
     </row>
-    <row r="662" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="662" spans="3:3">
       <c r="C662" s="2"/>
     </row>
-    <row r="663" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="663" spans="3:3">
       <c r="C663" s="2"/>
     </row>
-    <row r="664" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="664" spans="3:3">
       <c r="C664" s="2"/>
     </row>
-    <row r="665" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="665" spans="3:3">
       <c r="C665" s="2"/>
     </row>
-    <row r="666" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="666" spans="3:3">
       <c r="C666" s="2"/>
     </row>
-    <row r="667" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="667" spans="3:3">
       <c r="C667" s="2"/>
     </row>
-    <row r="668" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="668" spans="3:3">
       <c r="C668" s="2"/>
     </row>
-    <row r="669" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="669" spans="3:3">
       <c r="C669" s="2"/>
     </row>
-    <row r="670" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="670" spans="3:3">
       <c r="C670" s="2"/>
     </row>
-    <row r="671" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="671" spans="3:3">
       <c r="C671" s="2"/>
     </row>
-    <row r="672" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="672" spans="3:3">
       <c r="C672" s="2"/>
     </row>
-    <row r="673" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="673" spans="3:3">
       <c r="C673" s="2"/>
     </row>
-    <row r="674" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="674" spans="3:3">
       <c r="C674" s="2"/>
     </row>
-    <row r="675" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="675" spans="3:3">
       <c r="C675" s="2"/>
     </row>
-    <row r="676" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="676" spans="3:3">
       <c r="C676" s="2"/>
     </row>
-    <row r="677" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="677" spans="3:3">
       <c r="C677" s="2"/>
     </row>
-    <row r="678" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="678" spans="3:3">
       <c r="C678" s="2"/>
     </row>
-    <row r="679" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="679" spans="3:3">
       <c r="C679" s="2"/>
     </row>
-    <row r="680" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="680" spans="3:3">
       <c r="C680" s="2"/>
     </row>
-    <row r="681" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="681" spans="3:3">
       <c r="C681" s="2"/>
     </row>
-    <row r="682" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="682" spans="3:3">
       <c r="C682" s="2"/>
     </row>
-    <row r="683" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="683" spans="3:3">
       <c r="C683" s="2"/>
     </row>
-    <row r="684" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="684" spans="3:3">
       <c r="C684" s="2"/>
     </row>
-    <row r="685" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="685" spans="3:3">
       <c r="C685" s="2"/>
     </row>
-    <row r="686" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="686" spans="3:3">
       <c r="C686" s="2"/>
     </row>
-    <row r="687" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="687" spans="3:3">
       <c r="C687" s="2"/>
     </row>
-    <row r="688" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="688" spans="3:3">
       <c r="C688" s="2"/>
     </row>
-    <row r="689" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="689" spans="3:3">
       <c r="C689" s="2"/>
     </row>
-    <row r="690" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="690" spans="3:3">
       <c r="C690" s="2"/>
     </row>
-    <row r="691" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="691" spans="3:3">
       <c r="C691" s="2"/>
     </row>
-    <row r="692" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="692" spans="3:3">
       <c r="C692" s="2"/>
     </row>
-    <row r="693" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="693" spans="3:3">
       <c r="C693" s="2"/>
     </row>
-    <row r="694" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="694" spans="3:3">
       <c r="C694" s="2"/>
     </row>
-    <row r="695" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="695" spans="3:3">
       <c r="C695" s="2"/>
     </row>
-    <row r="696" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="696" spans="3:3">
       <c r="C696" s="2"/>
     </row>
-    <row r="697" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="697" spans="3:3">
       <c r="C697" s="2"/>
     </row>
-    <row r="698" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="698" spans="3:3">
       <c r="C698" s="2"/>
     </row>
-    <row r="699" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="699" spans="3:3">
       <c r="C699" s="2"/>
     </row>
-    <row r="700" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="700" spans="3:3">
       <c r="C700" s="2"/>
     </row>
-    <row r="701" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="701" spans="3:3">
       <c r="C701" s="2"/>
     </row>
-    <row r="702" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="702" spans="3:3">
       <c r="C702" s="2"/>
     </row>
-    <row r="703" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="703" spans="3:3">
       <c r="C703" s="2"/>
     </row>
-    <row r="704" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="704" spans="3:3">
       <c r="C704" s="2"/>
     </row>
-    <row r="705" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="705" spans="3:3">
       <c r="C705" s="2"/>
     </row>
-    <row r="706" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="706" spans="3:3">
       <c r="C706" s="2"/>
     </row>
-    <row r="707" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="707" spans="3:3">
       <c r="C707" s="2"/>
     </row>
-    <row r="708" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="708" spans="3:3">
       <c r="C708" s="2"/>
     </row>
-    <row r="709" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="709" spans="3:3">
       <c r="C709" s="2"/>
     </row>
-    <row r="710" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="710" spans="3:3">
       <c r="C710" s="2"/>
     </row>
-    <row r="711" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="711" spans="3:3">
       <c r="C711" s="2"/>
     </row>
-    <row r="712" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="712" spans="3:3">
       <c r="C712" s="2"/>
     </row>
-    <row r="713" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="713" spans="3:3">
       <c r="C713" s="2"/>
     </row>
-    <row r="714" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="714" spans="3:3">
       <c r="C714" s="2"/>
     </row>
-    <row r="715" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="715" spans="3:3">
       <c r="C715" s="2"/>
     </row>
-    <row r="716" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="716" spans="3:3">
       <c r="C716" s="2"/>
     </row>
-    <row r="717" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="717" spans="3:3">
       <c r="C717" s="2"/>
     </row>
-    <row r="718" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="718" spans="3:3">
       <c r="C718" s="2"/>
     </row>
-    <row r="719" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="719" spans="3:3">
       <c r="C719" s="2"/>
     </row>
-    <row r="720" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="720" spans="3:3">
       <c r="C720" s="2"/>
     </row>
-    <row r="721" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="721" spans="3:3">
       <c r="C721" s="2"/>
     </row>
-    <row r="722" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="722" spans="3:3">
       <c r="C722" s="2"/>
     </row>
-    <row r="723" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="723" spans="3:3">
       <c r="C723" s="2"/>
     </row>
-    <row r="724" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="724" spans="3:3">
       <c r="C724" s="2"/>
     </row>
-    <row r="725" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="725" spans="3:3">
       <c r="C725" s="2"/>
     </row>
-    <row r="726" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="726" spans="3:3">
       <c r="C726" s="2"/>
     </row>
-    <row r="727" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="727" spans="3:3">
       <c r="C727" s="2"/>
     </row>
-    <row r="728" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="728" spans="3:3">
       <c r="C728" s="2"/>
     </row>
-    <row r="729" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="729" spans="3:3">
       <c r="C729" s="2"/>
     </row>
-    <row r="730" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="730" spans="3:3">
       <c r="C730" s="2"/>
     </row>
-    <row r="731" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="731" spans="3:3">
       <c r="C731" s="2"/>
     </row>
-    <row r="732" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="732" spans="3:3">
       <c r="C732" s="2"/>
     </row>
-    <row r="733" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="733" spans="3:3">
       <c r="C733" s="2"/>
     </row>
-    <row r="734" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="734" spans="3:3">
       <c r="C734" s="2"/>
     </row>
-    <row r="735" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="735" spans="3:3">
       <c r="C735" s="2"/>
     </row>
-    <row r="736" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="736" spans="3:3">
       <c r="C736" s="2"/>
     </row>
-    <row r="737" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="737" spans="3:3">
       <c r="C737" s="2"/>
     </row>
-    <row r="738" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="738" spans="3:3">
       <c r="C738" s="2"/>
     </row>
-    <row r="739" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="739" spans="3:3">
       <c r="C739" s="2"/>
     </row>
-    <row r="740" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="740" spans="3:3">
       <c r="C740" s="2"/>
     </row>
-    <row r="741" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="741" spans="3:3">
       <c r="C741" s="2"/>
     </row>
-    <row r="742" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="742" spans="3:3">
       <c r="C742" s="2"/>
     </row>
-    <row r="743" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="743" spans="3:3">
       <c r="C743" s="2"/>
     </row>
-    <row r="744" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="744" spans="3:3">
       <c r="C744" s="2"/>
     </row>
-    <row r="745" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="745" spans="3:3">
       <c r="C745" s="2"/>
     </row>
-    <row r="746" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="746" spans="3:3">
       <c r="C746" s="2"/>
     </row>
-    <row r="747" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="747" spans="3:3">
       <c r="C747" s="2"/>
     </row>
-    <row r="748" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="748" spans="3:3">
       <c r="C748" s="2"/>
     </row>
-    <row r="749" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="749" spans="3:3">
       <c r="C749" s="2"/>
     </row>
-    <row r="750" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="750" spans="3:3">
       <c r="C750" s="2"/>
     </row>
-    <row r="751" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="751" spans="3:3">
       <c r="C751" s="2"/>
     </row>
-    <row r="752" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="752" spans="3:3">
       <c r="C752" s="2"/>
     </row>
-    <row r="753" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="753" spans="3:3">
       <c r="C753" s="2"/>
     </row>
-    <row r="754" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="754" spans="3:3">
       <c r="C754" s="2"/>
     </row>
-    <row r="755" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="755" spans="3:3">
       <c r="C755" s="2"/>
     </row>
-    <row r="756" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="756" spans="3:3">
       <c r="C756" s="2"/>
     </row>
-    <row r="757" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="757" spans="3:3">
       <c r="C757" s="2"/>
     </row>
-    <row r="758" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="758" spans="3:3">
       <c r="C758" s="2"/>
     </row>
-    <row r="759" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="759" spans="3:3">
       <c r="C759" s="2"/>
     </row>
-    <row r="760" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="760" spans="3:3">
       <c r="C760" s="2"/>
     </row>
-    <row r="761" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="761" spans="3:3">
       <c r="C761" s="2"/>
     </row>
-    <row r="762" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="762" spans="3:3">
       <c r="C762" s="2"/>
     </row>
-    <row r="763" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="763" spans="3:3">
       <c r="C763" s="2"/>
     </row>
-    <row r="764" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="764" spans="3:3">
       <c r="C764" s="2"/>
     </row>
-    <row r="765" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="765" spans="3:3">
       <c r="C765" s="2"/>
     </row>
-    <row r="766" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="766" spans="3:3">
       <c r="C766" s="2"/>
     </row>
-    <row r="767" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="767" spans="3:3">
       <c r="C767" s="2"/>
     </row>
-    <row r="768" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="768" spans="3:3">
       <c r="C768" s="2"/>
     </row>
-    <row r="769" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="769" spans="3:3">
       <c r="C769" s="2"/>
     </row>
-    <row r="770" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="770" spans="3:3">
       <c r="C770" s="2"/>
     </row>
-    <row r="771" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="771" spans="3:3">
       <c r="C771" s="2"/>
     </row>
-    <row r="772" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="772" spans="3:3">
       <c r="C772" s="2"/>
     </row>
-    <row r="773" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="773" spans="3:3">
       <c r="C773" s="2"/>
     </row>
-    <row r="774" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="774" spans="3:3">
       <c r="C774" s="2"/>
     </row>
-    <row r="775" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="775" spans="3:3">
       <c r="C775" s="2"/>
     </row>
-    <row r="776" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="776" spans="3:3">
       <c r="C776" s="2"/>
     </row>
-    <row r="777" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="777" spans="3:3">
       <c r="C777" s="2"/>
     </row>
-    <row r="778" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="778" spans="3:3">
       <c r="C778" s="2"/>
     </row>
-    <row r="779" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="779" spans="3:3">
       <c r="C779" s="2"/>
     </row>
-    <row r="780" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="780" spans="3:3">
       <c r="C780" s="2"/>
     </row>
-    <row r="781" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="781" spans="3:3">
       <c r="C781" s="2"/>
     </row>
-    <row r="782" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="782" spans="3:3">
       <c r="C782" s="2"/>
     </row>
-    <row r="783" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="783" spans="3:3">
       <c r="C783" s="2"/>
     </row>
-    <row r="784" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="784" spans="3:3">
       <c r="C784" s="2"/>
     </row>
-    <row r="785" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="785" spans="3:3">
       <c r="C785" s="2"/>
     </row>
-    <row r="786" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="786" spans="3:3">
       <c r="C786" s="2"/>
     </row>
-    <row r="787" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="787" spans="3:3">
       <c r="C787" s="2"/>
     </row>
-    <row r="788" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="788" spans="3:3">
       <c r="C788" s="2"/>
     </row>
-    <row r="789" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="789" spans="3:3">
       <c r="C789" s="2"/>
     </row>
-    <row r="790" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="790" spans="3:3">
       <c r="C790" s="2"/>
     </row>
-    <row r="791" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="791" spans="3:3">
       <c r="C791" s="2"/>
     </row>
-    <row r="792" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="792" spans="3:3">
       <c r="C792" s="2"/>
     </row>
-    <row r="793" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="793" spans="3:3">
       <c r="C793" s="2"/>
     </row>
-    <row r="794" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="794" spans="3:3">
       <c r="C794" s="2"/>
     </row>
-    <row r="795" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="795" spans="3:3">
       <c r="C795" s="2"/>
     </row>
-    <row r="796" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="796" spans="3:3">
       <c r="C796" s="2"/>
     </row>
-    <row r="797" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="797" spans="3:3">
       <c r="C797" s="2"/>
     </row>
-    <row r="798" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="798" spans="3:3">
       <c r="C798" s="2"/>
     </row>
-    <row r="799" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="799" spans="3:3">
       <c r="C799" s="2"/>
     </row>
-    <row r="800" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="800" spans="3:3">
       <c r="C800" s="2"/>
     </row>
-    <row r="801" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="801" spans="3:3">
       <c r="C801" s="2"/>
     </row>
-    <row r="802" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="802" spans="3:3">
       <c r="C802" s="2"/>
     </row>
-    <row r="803" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="803" spans="3:3">
       <c r="C803" s="2"/>
     </row>
-    <row r="804" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="804" spans="3:3">
       <c r="C804" s="2"/>
     </row>
-    <row r="805" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="805" spans="3:3">
       <c r="C805" s="2"/>
     </row>
-    <row r="806" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="806" spans="3:3">
       <c r="C806" s="2"/>
     </row>
-    <row r="807" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="807" spans="3:3">
       <c r="C807" s="2"/>
     </row>
-    <row r="808" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="808" spans="3:3">
       <c r="C808" s="2"/>
     </row>
-    <row r="809" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="809" spans="3:3">
       <c r="C809" s="2"/>
     </row>
-    <row r="810" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="810" spans="3:3">
       <c r="C810" s="2"/>
     </row>
-    <row r="811" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="811" spans="3:3">
       <c r="C811" s="2"/>
     </row>
-    <row r="812" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="812" spans="3:3">
       <c r="C812" s="2"/>
     </row>
-    <row r="813" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="813" spans="3:3">
       <c r="C813" s="2"/>
     </row>
-    <row r="814" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="814" spans="3:3">
       <c r="C814" s="2"/>
     </row>
-    <row r="815" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="815" spans="3:3">
       <c r="C815" s="2"/>
     </row>
-    <row r="816" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="816" spans="3:3">
       <c r="C816" s="2"/>
     </row>
-    <row r="817" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="817" spans="3:3">
       <c r="C817" s="2"/>
     </row>
-    <row r="818" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="818" spans="3:3">
       <c r="C818" s="2"/>
     </row>
-    <row r="819" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="819" spans="3:3">
       <c r="C819" s="2"/>
     </row>
-    <row r="820" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="820" spans="3:3">
       <c r="C820" s="2"/>
     </row>
-    <row r="821" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="821" spans="3:3">
       <c r="C821" s="2"/>
     </row>
-    <row r="822" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="822" spans="3:3">
       <c r="C822" s="2"/>
     </row>
-    <row r="823" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="823" spans="3:3">
       <c r="C823" s="2"/>
     </row>
-    <row r="824" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="824" spans="3:3">
       <c r="C824" s="2"/>
     </row>
-    <row r="825" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="825" spans="3:3">
       <c r="C825" s="2"/>
     </row>
-    <row r="826" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="826" spans="3:3">
       <c r="C826" s="2"/>
     </row>
-    <row r="827" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="827" spans="3:3">
       <c r="C827" s="2"/>
     </row>
-    <row r="828" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="828" spans="3:3">
       <c r="C828" s="2"/>
     </row>
-    <row r="829" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="829" spans="3:3">
       <c r="C829" s="2"/>
     </row>
-    <row r="830" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="830" spans="3:3">
       <c r="C830" s="2"/>
     </row>
-    <row r="831" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="831" spans="3:3">
       <c r="C831" s="2"/>
     </row>
-    <row r="832" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="832" spans="3:3">
       <c r="C832" s="2"/>
     </row>
-    <row r="833" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="833" spans="3:3">
       <c r="C833" s="2"/>
     </row>
-    <row r="834" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="834" spans="3:3">
       <c r="C834" s="2"/>
     </row>
-    <row r="835" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="835" spans="3:3">
       <c r="C835" s="2"/>
     </row>
-    <row r="836" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="836" spans="3:3">
       <c r="C836" s="2"/>
     </row>
-    <row r="837" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="837" spans="3:3">
       <c r="C837" s="2"/>
     </row>
-    <row r="838" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="838" spans="3:3">
       <c r="C838" s="2"/>
     </row>
-    <row r="839" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="839" spans="3:3">
       <c r="C839" s="2"/>
     </row>
-    <row r="840" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="840" spans="3:3">
       <c r="C840" s="2"/>
     </row>
-    <row r="841" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="841" spans="3:3">
       <c r="C841" s="2"/>
     </row>
-    <row r="842" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="842" spans="3:3">
       <c r="C842" s="2"/>
     </row>
-    <row r="843" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="843" spans="3:3">
       <c r="C843" s="2"/>
     </row>
-    <row r="844" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="844" spans="3:3">
       <c r="C844" s="2"/>
     </row>
-    <row r="845" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="845" spans="3:3">
       <c r="C845" s="2"/>
     </row>
-    <row r="846" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="846" spans="3:3">
       <c r="C846" s="2"/>
     </row>
-    <row r="847" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="847" spans="3:3">
       <c r="C847" s="2"/>
     </row>
-    <row r="848" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="848" spans="3:3">
       <c r="C848" s="2"/>
     </row>
-    <row r="849" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="849" spans="3:3">
       <c r="C849" s="2"/>
     </row>
-    <row r="850" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="850" spans="3:3">
       <c r="C850" s="2"/>
     </row>
-    <row r="851" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="851" spans="3:3">
       <c r="C851" s="2"/>
     </row>
-    <row r="852" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="852" spans="3:3">
       <c r="C852" s="2"/>
     </row>
-    <row r="853" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="853" spans="3:3">
       <c r="C853" s="2"/>
     </row>
-    <row r="854" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="854" spans="3:3">
       <c r="C854" s="2"/>
     </row>
-    <row r="855" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="855" spans="3:3">
       <c r="C855" s="2"/>
     </row>
-    <row r="856" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="856" spans="3:3">
       <c r="C856" s="2"/>
     </row>
-    <row r="857" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="857" spans="3:3">
       <c r="C857" s="2"/>
     </row>
-    <row r="858" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="858" spans="3:3">
       <c r="C858" s="2"/>
     </row>
-    <row r="859" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="859" spans="3:3">
       <c r="C859" s="2"/>
     </row>
-    <row r="860" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="860" spans="3:3">
       <c r="C860" s="2"/>
     </row>
-    <row r="861" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="861" spans="3:3">
       <c r="C861" s="2"/>
     </row>
-    <row r="862" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="862" spans="3:3">
       <c r="C862" s="2"/>
     </row>
-    <row r="863" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="863" spans="3:3">
       <c r="C863" s="2"/>
     </row>
-    <row r="864" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="864" spans="3:3">
       <c r="C864" s="2"/>
     </row>
-    <row r="865" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="865" spans="3:3">
       <c r="C865" s="2"/>
     </row>
-    <row r="866" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="866" spans="3:3">
       <c r="C866" s="2"/>
     </row>
-    <row r="867" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="867" spans="3:3">
       <c r="C867" s="2"/>
     </row>
-    <row r="868" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="868" spans="3:3">
       <c r="C868" s="2"/>
     </row>
-    <row r="869" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="869" spans="3:3">
       <c r="C869" s="2"/>
     </row>
-    <row r="870" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="870" spans="3:3">
       <c r="C870" s="2"/>
     </row>
-    <row r="871" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="871" spans="3:3">
       <c r="C871" s="2"/>
     </row>
-    <row r="872" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="872" spans="3:3">
       <c r="C872" s="2"/>
     </row>
-    <row r="873" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="873" spans="3:3">
       <c r="C873" s="2"/>
     </row>
-    <row r="874" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="874" spans="3:3">
       <c r="C874" s="2"/>
     </row>
-    <row r="875" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="875" spans="3:3">
       <c r="C875" s="2"/>
     </row>
-    <row r="876" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="876" spans="3:3">
       <c r="C876" s="2"/>
     </row>
-    <row r="877" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="877" spans="3:3">
       <c r="C877" s="2"/>
     </row>
-    <row r="878" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="878" spans="3:3">
       <c r="C878" s="2"/>
     </row>
-    <row r="879" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="879" spans="3:3">
       <c r="C879" s="2"/>
     </row>
-    <row r="880" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="880" spans="3:3">
       <c r="C880" s="2"/>
     </row>
-    <row r="881" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="881" spans="3:3">
       <c r="C881" s="2"/>
     </row>
-    <row r="882" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="882" spans="3:3">
       <c r="C882" s="2"/>
     </row>
-    <row r="883" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="883" spans="3:3">
       <c r="C883" s="2"/>
     </row>
-    <row r="884" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="884" spans="3:3">
       <c r="C884" s="2"/>
     </row>
-    <row r="885" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="885" spans="3:3">
       <c r="C885" s="2"/>
     </row>
-    <row r="886" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="886" spans="3:3">
       <c r="C886" s="2"/>
     </row>
-    <row r="887" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="887" spans="3:3">
       <c r="C887" s="2"/>
     </row>
-    <row r="888" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="888" spans="3:3">
       <c r="C888" s="2"/>
     </row>
-    <row r="889" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="889" spans="3:3">
       <c r="C889" s="2"/>
     </row>
-    <row r="890" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="890" spans="3:3">
       <c r="C890" s="2"/>
     </row>
-    <row r="891" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="891" spans="3:3">
       <c r="C891" s="2"/>
     </row>
-    <row r="892" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="892" spans="3:3">
       <c r="C892" s="2"/>
     </row>
-    <row r="893" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="893" spans="3:3">
       <c r="C893" s="2"/>
     </row>
-    <row r="894" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="894" spans="3:3">
       <c r="C894" s="2"/>
     </row>
-    <row r="895" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="895" spans="3:3">
       <c r="C895" s="2"/>
     </row>
-    <row r="896" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="896" spans="3:3">
       <c r="C896" s="2"/>
     </row>
-    <row r="897" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="897" spans="3:3">
       <c r="C897" s="2"/>
     </row>
-    <row r="898" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="898" spans="3:3">
       <c r="C898" s="2"/>
     </row>
-    <row r="899" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="899" spans="3:3">
       <c r="C899" s="2"/>
     </row>
-    <row r="900" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="900" spans="3:3">
       <c r="C900" s="2"/>
     </row>
-    <row r="901" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="901" spans="3:3">
       <c r="C901" s="2"/>
     </row>
-    <row r="902" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="902" spans="3:3">
       <c r="C902" s="2"/>
     </row>
-    <row r="903" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="903" spans="3:3">
       <c r="C903" s="2"/>
     </row>
-    <row r="904" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="904" spans="3:3">
       <c r="C904" s="2"/>
     </row>
-    <row r="905" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="905" spans="3:3">
       <c r="C905" s="2"/>
     </row>
-    <row r="906" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="906" spans="3:3">
       <c r="C906" s="2"/>
     </row>
-    <row r="907" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="907" spans="3:3">
       <c r="C907" s="2"/>
     </row>
-    <row r="908" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="908" spans="3:3">
       <c r="C908" s="2"/>
     </row>
-    <row r="909" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="909" spans="3:3">
       <c r="C909" s="2"/>
     </row>
-    <row r="910" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="910" spans="3:3">
       <c r="C910" s="2"/>
     </row>
-    <row r="911" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="911" spans="3:3">
       <c r="C911" s="2"/>
     </row>
-    <row r="912" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="912" spans="3:3">
       <c r="C912" s="2"/>
     </row>
-    <row r="913" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="913" spans="3:3">
       <c r="C913" s="2"/>
     </row>
-    <row r="914" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="914" spans="3:3">
       <c r="C914" s="2"/>
     </row>
-    <row r="915" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="915" spans="3:3">
       <c r="C915" s="2"/>
     </row>
-    <row r="916" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="916" spans="3:3">
       <c r="C916" s="2"/>
     </row>
-    <row r="917" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="917" spans="3:3">
       <c r="C917" s="2"/>
     </row>
-    <row r="918" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="918" spans="3:3">
       <c r="C918" s="2"/>
     </row>
-    <row r="919" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="919" spans="3:3">
       <c r="C919" s="2"/>
     </row>
-    <row r="920" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="920" spans="3:3">
       <c r="C920" s="2"/>
     </row>
-    <row r="921" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="921" spans="3:3">
       <c r="C921" s="2"/>
     </row>
-    <row r="922" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="922" spans="3:3">
       <c r="C922" s="2"/>
     </row>
-    <row r="923" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="923" spans="3:3">
       <c r="C923" s="2"/>
     </row>
-    <row r="924" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="924" spans="3:3">
       <c r="C924" s="2"/>
     </row>
-    <row r="925" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="925" spans="3:3">
       <c r="C925" s="2"/>
     </row>
-    <row r="926" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="926" spans="3:3">
       <c r="C926" s="2"/>
     </row>
-    <row r="927" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="927" spans="3:3">
       <c r="C927" s="2"/>
     </row>
-    <row r="928" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="928" spans="3:3">
       <c r="C928" s="2"/>
     </row>
-    <row r="929" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="929" spans="3:3">
       <c r="C929" s="2"/>
     </row>
-    <row r="930" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="930" spans="3:3">
       <c r="C930" s="2"/>
     </row>
-    <row r="931" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="931" spans="3:3">
       <c r="C931" s="2"/>
     </row>
-    <row r="932" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="932" spans="3:3">
       <c r="C932" s="2"/>
     </row>
-    <row r="933" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="933" spans="3:3">
       <c r="C933" s="2"/>
     </row>
-    <row r="934" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="934" spans="3:3">
       <c r="C934" s="2"/>
     </row>
-    <row r="935" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="935" spans="3:3">
       <c r="C935" s="2"/>
     </row>
-    <row r="936" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="936" spans="3:3">
       <c r="C936" s="2"/>
     </row>
-    <row r="937" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="937" spans="3:3">
       <c r="C937" s="2"/>
     </row>
-    <row r="938" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="938" spans="3:3">
       <c r="C938" s="2"/>
     </row>
-    <row r="939" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="939" spans="3:3">
       <c r="C939" s="2"/>
     </row>
-    <row r="940" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="940" spans="3:3">
       <c r="C940" s="2"/>
     </row>
-    <row r="941" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="941" spans="3:3">
       <c r="C941" s="2"/>
     </row>
-    <row r="942" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="942" spans="3:3">
       <c r="C942" s="2"/>
     </row>
-    <row r="943" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="943" spans="3:3">
       <c r="C943" s="2"/>
     </row>
-    <row r="944" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="944" spans="3:3">
       <c r="C944" s="2"/>
     </row>
-    <row r="945" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="945" spans="3:3">
       <c r="C945" s="2"/>
     </row>
-    <row r="946" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="946" spans="3:3">
       <c r="C946" s="2"/>
     </row>
-    <row r="947" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="947" spans="3:3">
       <c r="C947" s="2"/>
     </row>
-    <row r="948" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="948" spans="3:3">
       <c r="C948" s="2"/>
     </row>
-    <row r="949" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="949" spans="3:3">
       <c r="C949" s="2"/>
     </row>
-    <row r="950" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="950" spans="3:3">
       <c r="C950" s="2"/>
     </row>
-    <row r="951" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="951" spans="3:3">
       <c r="C951" s="2"/>
     </row>
-    <row r="952" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="952" spans="3:3">
       <c r="C952" s="2"/>
     </row>
-    <row r="953" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="953" spans="3:3">
       <c r="C953" s="2"/>
     </row>
-    <row r="954" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="954" spans="3:3">
       <c r="C954" s="2"/>
     </row>
-    <row r="955" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="955" spans="3:3">
       <c r="C955" s="2"/>
     </row>
-    <row r="956" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="956" spans="3:3">
       <c r="C956" s="2"/>
     </row>
-    <row r="957" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="957" spans="3:3">
       <c r="C957" s="2"/>
     </row>
-    <row r="958" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="958" spans="3:3">
       <c r="C958" s="2"/>
     </row>
-    <row r="959" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="959" spans="3:3">
       <c r="C959" s="2"/>
     </row>
-    <row r="960" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="960" spans="3:3">
       <c r="C960" s="2"/>
     </row>
-    <row r="961" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="961" spans="3:3">
       <c r="C961" s="2"/>
     </row>
-    <row r="962" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="962" spans="3:3">
       <c r="C962" s="2"/>
     </row>
-    <row r="963" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="963" spans="3:3">
       <c r="C963" s="2"/>
     </row>
-    <row r="964" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="964" spans="3:3">
       <c r="C964" s="2"/>
     </row>
-    <row r="965" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="965" spans="3:3">
       <c r="C965" s="2"/>
     </row>
-    <row r="966" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="966" spans="3:3">
       <c r="C966" s="2"/>
     </row>
-    <row r="967" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="967" spans="3:3">
       <c r="C967" s="2"/>
     </row>
-    <row r="968" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="968" spans="3:3">
       <c r="C968" s="2"/>
     </row>
-    <row r="969" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="969" spans="3:3">
       <c r="C969" s="2"/>
     </row>
-    <row r="970" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="970" spans="3:3">
       <c r="C970" s="2"/>
     </row>
-    <row r="971" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="971" spans="3:3">
       <c r="C971" s="2"/>
     </row>
-    <row r="972" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="972" spans="3:3">
       <c r="C972" s="2"/>
     </row>
-    <row r="973" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="973" spans="3:3">
       <c r="C973" s="2"/>
     </row>
-    <row r="974" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="974" spans="3:3">
       <c r="C974" s="2"/>
     </row>
-    <row r="975" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="975" spans="3:3">
       <c r="C975" s="2"/>
     </row>
-    <row r="976" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="976" spans="3:3">
       <c r="C976" s="2"/>
     </row>
-    <row r="977" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="977" spans="3:3">
       <c r="C977" s="2"/>
     </row>
-    <row r="978" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="978" spans="3:3">
       <c r="C978" s="2"/>
     </row>
-    <row r="979" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="979" spans="3:3">
       <c r="C979" s="2"/>
     </row>
-    <row r="980" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="980" spans="3:3">
       <c r="C980" s="2"/>
     </row>
-    <row r="981" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="981" spans="3:3">
       <c r="C981" s="2"/>
     </row>
-    <row r="982" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="982" spans="3:3">
       <c r="C982" s="2"/>
     </row>
-    <row r="983" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="983" spans="3:3">
       <c r="C983" s="2"/>
     </row>
-    <row r="984" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="984" spans="3:3">
       <c r="C984" s="2"/>
     </row>
-    <row r="985" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="985" spans="3:3">
       <c r="C985" s="2"/>
     </row>
-    <row r="986" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="986" spans="3:3">
       <c r="C986" s="2"/>
     </row>
-    <row r="987" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="987" spans="3:3">
       <c r="C987" s="2"/>
     </row>
-    <row r="988" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="988" spans="3:3">
       <c r="C988" s="2"/>
     </row>
-    <row r="989" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="989" spans="3:3">
       <c r="C989" s="2"/>
     </row>
-    <row r="990" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="990" spans="3:3">
       <c r="C990" s="2"/>
     </row>
-    <row r="991" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="991" spans="3:3">
       <c r="C991" s="2"/>
     </row>
-    <row r="992" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="992" spans="3:3">
       <c r="C992" s="2"/>
     </row>
-    <row r="993" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="993" spans="3:3">
       <c r="C993" s="2"/>
     </row>
-    <row r="994" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="994" spans="3:3">
       <c r="C994" s="2"/>
     </row>
-    <row r="995" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="995" spans="3:3">
       <c r="C995" s="2"/>
     </row>
-    <row r="996" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="996" spans="3:3">
       <c r="C996" s="2"/>
     </row>
-    <row r="997" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="997" spans="3:3">
       <c r="C997" s="2"/>
     </row>
-    <row r="998" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="998" spans="3:3">
       <c r="C998" s="2"/>
     </row>
-    <row r="999" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="999" spans="3:3">
       <c r="C999" s="2"/>
     </row>
-    <row r="1000" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1000" spans="3:3">
       <c r="C1000" s="2"/>
     </row>
-    <row r="1001" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1001" spans="3:3">
       <c r="C1001" s="2"/>
     </row>
-    <row r="1002" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1002" spans="3:3">
       <c r="C1002" s="2"/>
     </row>
-    <row r="1003" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1003" spans="3:3">
       <c r="C1003" s="2"/>
     </row>
-    <row r="1004" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1004" spans="3:3">
       <c r="C1004" s="2"/>
     </row>
-    <row r="1005" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1005" spans="3:3">
       <c r="C1005" s="2"/>
     </row>
-    <row r="1006" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1006" spans="3:3">
       <c r="C1006" s="2"/>
     </row>
-    <row r="1007" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1007" spans="3:3">
       <c r="C1007" s="2"/>
     </row>
-    <row r="1008" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1008" spans="3:3">
       <c r="C1008" s="2"/>
     </row>
-    <row r="1009" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1009" spans="3:3">
       <c r="C1009" s="2"/>
     </row>
-    <row r="1010" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1010" spans="3:3">
       <c r="C1010" s="2"/>
     </row>
-    <row r="1011" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1011" spans="3:3">
       <c r="C1011" s="2"/>
     </row>
-    <row r="1012" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1012" spans="3:3">
       <c r="C1012" s="2"/>
     </row>
-    <row r="1013" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1013" spans="3:3">
       <c r="C1013" s="2"/>
     </row>
-    <row r="1014" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1014" spans="3:3">
       <c r="C1014" s="2"/>
     </row>
-    <row r="1015" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1015" spans="3:3">
       <c r="C1015" s="2"/>
     </row>
-    <row r="1016" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1016" spans="3:3">
       <c r="C1016" s="2"/>
     </row>
-    <row r="1017" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1017" spans="3:3">
       <c r="C1017" s="2"/>
     </row>
-    <row r="1018" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1018" spans="3:3">
       <c r="C1018" s="2"/>
     </row>
-    <row r="1019" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1019" spans="3:3">
       <c r="C1019" s="2"/>
     </row>
-    <row r="1020" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1020" spans="3:3">
       <c r="C1020" s="2"/>
     </row>
-    <row r="1021" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1021" spans="3:3">
       <c r="C1021" s="2"/>
     </row>
-    <row r="1022" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1022" spans="3:3">
       <c r="C1022" s="2"/>
     </row>
-    <row r="1023" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1023" spans="3:3">
       <c r="C1023" s="2"/>
     </row>
-    <row r="1024" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1024" spans="3:3">
       <c r="C1024" s="2"/>
     </row>
-    <row r="1025" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1025" spans="3:3">
       <c r="C1025" s="2"/>
     </row>
-    <row r="1026" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1026" spans="3:3">
       <c r="C1026" s="2"/>
     </row>
-    <row r="1027" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1027" spans="3:3">
       <c r="C1027" s="2"/>
     </row>
-    <row r="1028" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1028" spans="3:3">
       <c r="C1028" s="2"/>
     </row>
-    <row r="1029" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1029" spans="3:3">
       <c r="C1029" s="2"/>
     </row>
-    <row r="1030" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1030" spans="3:3">
       <c r="C1030" s="2"/>
     </row>
-    <row r="1031" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1031" spans="3:3">
       <c r="C1031" s="2"/>
     </row>
-    <row r="1032" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1032" spans="3:3">
       <c r="C1032" s="2"/>
     </row>
-    <row r="1033" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1033" spans="3:3">
       <c r="C1033" s="2"/>
     </row>
-    <row r="1034" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1034" spans="3:3">
       <c r="C1034" s="2"/>
     </row>
-    <row r="1035" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1035" spans="3:3">
       <c r="C1035" s="2"/>
     </row>
-    <row r="1036" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1036" spans="3:3">
       <c r="C1036" s="2"/>
     </row>
-    <row r="1037" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1037" spans="3:3">
       <c r="C1037" s="2"/>
     </row>
-    <row r="1038" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1038" spans="3:3">
       <c r="C1038" s="2"/>
     </row>
-    <row r="1039" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1039" spans="3:3">
       <c r="C1039" s="2"/>
     </row>
-    <row r="1040" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1040" spans="3:3">
       <c r="C1040" s="2"/>
     </row>
-    <row r="1041" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1041" spans="3:3">
       <c r="C1041" s="2"/>
     </row>
-    <row r="1042" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1042" spans="3:3">
       <c r="C1042" s="2"/>
     </row>
-    <row r="1043" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1043" spans="3:3">
       <c r="C1043" s="2"/>
     </row>
-    <row r="1044" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1044" spans="3:3">
       <c r="C1044" s="2"/>
     </row>
-    <row r="1045" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1045" spans="3:3">
       <c r="C1045" s="2"/>
     </row>
-    <row r="1046" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1046" spans="3:3">
       <c r="C1046" s="2"/>
     </row>
-    <row r="1047" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1047" spans="3:3">
       <c r="C1047" s="2"/>
     </row>
-    <row r="1048" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1048" spans="3:3">
       <c r="C1048" s="2"/>
     </row>
-    <row r="1049" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1049" spans="3:3">
       <c r="C1049" s="2"/>
     </row>
-    <row r="1050" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1050" spans="3:3">
       <c r="C1050" s="2"/>
     </row>
-    <row r="1051" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1051" spans="3:3">
       <c r="C1051" s="2"/>
     </row>
-    <row r="1052" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1052" spans="3:3">
       <c r="C1052" s="2"/>
     </row>
-    <row r="1053" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1053" spans="3:3">
       <c r="C1053" s="2"/>
     </row>
-    <row r="1054" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1054" spans="3:3">
       <c r="C1054" s="2"/>
     </row>
-    <row r="1055" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1055" spans="3:3">
       <c r="C1055" s="2"/>
     </row>
-    <row r="1056" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1056" spans="3:3">
       <c r="C1056" s="2"/>
     </row>
-    <row r="1057" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1057" spans="3:3">
       <c r="C1057" s="2"/>
     </row>
-    <row r="1058" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1058" spans="3:3">
       <c r="C1058" s="2"/>
     </row>
-    <row r="1059" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1059" spans="3:3">
       <c r="C1059" s="2"/>
     </row>
-    <row r="1060" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1060" spans="3:3">
       <c r="C1060" s="2"/>
     </row>
-    <row r="1061" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1061" spans="3:3">
       <c r="C1061" s="2"/>
     </row>
-    <row r="1062" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1062" spans="3:3">
       <c r="C1062" s="2"/>
     </row>
-    <row r="1063" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1063" spans="3:3">
       <c r="C1063" s="2"/>
     </row>
-    <row r="1064" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1064" spans="3:3">
       <c r="C1064" s="2"/>
     </row>
-    <row r="1065" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1065" spans="3:3">
       <c r="C1065" s="2"/>
     </row>
-    <row r="1066" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1066" spans="3:3">
       <c r="C1066" s="2"/>
     </row>
-    <row r="1067" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1067" spans="3:3">
       <c r="C1067" s="2"/>
     </row>
-    <row r="1068" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1068" spans="3:3">
       <c r="C1068" s="2"/>
     </row>
-    <row r="1069" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1069" spans="3:3">
       <c r="C1069" s="2"/>
     </row>
-    <row r="1070" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1070" spans="3:3">
       <c r="C1070" s="2"/>
     </row>
-    <row r="1071" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1071" spans="3:3">
       <c r="C1071" s="2"/>
     </row>
-    <row r="1072" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1072" spans="3:3">
       <c r="C1072" s="2"/>
     </row>
-    <row r="1073" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1073" spans="3:3">
       <c r="C1073" s="2"/>
     </row>
-    <row r="1074" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1074" spans="3:3">
       <c r="C1074" s="2"/>
     </row>
-    <row r="1075" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1075" spans="3:3">
       <c r="C1075" s="2"/>
     </row>
-    <row r="1076" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1076" spans="3:3">
       <c r="C1076" s="2"/>
     </row>
-    <row r="1077" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1077" spans="3:3">
       <c r="C1077" s="2"/>
     </row>
-    <row r="1078" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1078" spans="3:3">
       <c r="C1078" s="2"/>
     </row>
-    <row r="1079" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1079" spans="3:3">
       <c r="C1079" s="2"/>
     </row>
-    <row r="1080" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1080" spans="3:3">
       <c r="C1080" s="2"/>
     </row>
-    <row r="1081" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1081" spans="3:3">
       <c r="C1081" s="2"/>
     </row>
-    <row r="1082" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1082" spans="3:3">
       <c r="C1082" s="2"/>
     </row>
-    <row r="1083" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1083" spans="3:3">
       <c r="C1083" s="2"/>
     </row>
-    <row r="1084" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1084" spans="3:3">
       <c r="C1084" s="2"/>
     </row>
-    <row r="1085" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1085" spans="3:3">
       <c r="C1085" s="2"/>
     </row>
-    <row r="1086" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1086" spans="3:3">
       <c r="C1086" s="2"/>
     </row>
-    <row r="1087" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1087" spans="3:3">
       <c r="C1087" s="2"/>
     </row>
-    <row r="1088" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1088" spans="3:3">
       <c r="C1088" s="2"/>
     </row>
-    <row r="1089" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1089" spans="3:3">
       <c r="C1089" s="2"/>
     </row>
-    <row r="1090" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1090" spans="3:3">
       <c r="C1090" s="2"/>
     </row>
-    <row r="1091" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1091" spans="3:3">
       <c r="C1091" s="2"/>
     </row>
-    <row r="1092" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1092" spans="3:3">
       <c r="C1092" s="2"/>
     </row>
-    <row r="1093" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1093" spans="3:3">
       <c r="C1093" s="2"/>
     </row>
-    <row r="1094" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1094" spans="3:3">
       <c r="C1094" s="2"/>
     </row>
-    <row r="1095" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1095" spans="3:3">
       <c r="C1095" s="2"/>
     </row>
-    <row r="1096" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1096" spans="3:3">
       <c r="C1096" s="2"/>
     </row>
-    <row r="1097" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1097" spans="3:3">
       <c r="C1097" s="2"/>
     </row>
-    <row r="1098" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1098" spans="3:3">
       <c r="C1098" s="2"/>
     </row>
-    <row r="1099" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1099" spans="3:3">
       <c r="C1099" s="2"/>
     </row>
-    <row r="1100" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1100" spans="3:3">
       <c r="C1100" s="2"/>
     </row>
-    <row r="1101" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1101" spans="3:3">
       <c r="C1101" s="2"/>
     </row>
-    <row r="1102" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1102" spans="3:3">
       <c r="C1102" s="2"/>
     </row>
-    <row r="1103" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1103" spans="3:3">
       <c r="C1103" s="2"/>
     </row>
-    <row r="1104" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1104" spans="3:3">
       <c r="C1104" s="2"/>
     </row>
-    <row r="1105" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1105" spans="3:3">
       <c r="C1105" s="2"/>
     </row>
-    <row r="1106" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1106" spans="3:3">
       <c r="C1106" s="2"/>
     </row>
-    <row r="1107" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1107" spans="3:3">
       <c r="C1107" s="2"/>
     </row>
-    <row r="1108" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1108" spans="3:3">
       <c r="C1108" s="2"/>
     </row>
-    <row r="1109" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1109" spans="3:3">
       <c r="C1109" s="2"/>
     </row>
-    <row r="1110" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1110" spans="3:3">
       <c r="C1110" s="2"/>
     </row>
-    <row r="1111" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1111" spans="3:3">
       <c r="C1111" s="2"/>
     </row>
-    <row r="1112" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1112" spans="3:3">
       <c r="C1112" s="2"/>
     </row>
-    <row r="1113" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1113" spans="3:3">
       <c r="C1113" s="2"/>
     </row>
-    <row r="1114" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1114" spans="3:3">
       <c r="C1114" s="2"/>
     </row>
-    <row r="1115" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1115" spans="3:3">
       <c r="C1115" s="2"/>
     </row>
-    <row r="1116" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1116" spans="3:3">
       <c r="C1116" s="2"/>
     </row>
-    <row r="1117" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1117" spans="3:3">
       <c r="C1117" s="2"/>
     </row>
-    <row r="1118" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1118" spans="3:3">
       <c r="C1118" s="2"/>
     </row>
-    <row r="1119" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1119" spans="3:3">
       <c r="C1119" s="2"/>
     </row>
-    <row r="1120" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1120" spans="3:3">
       <c r="C1120" s="2"/>
     </row>
-    <row r="1121" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1121" spans="3:3">
       <c r="C1121" s="2"/>
     </row>
-    <row r="1122" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1122" spans="3:3">
       <c r="C1122" s="2"/>
     </row>
-    <row r="1123" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1123" spans="3:3">
       <c r="C1123" s="2"/>
     </row>
-    <row r="1124" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1124" spans="3:3">
       <c r="C1124" s="2"/>
     </row>
-    <row r="1125" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1125" spans="3:3">
       <c r="C1125" s="2"/>
     </row>
-    <row r="1126" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1126" spans="3:3">
       <c r="C1126" s="2"/>
     </row>
-    <row r="1127" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1127" spans="3:3">
       <c r="C1127" s="2"/>
     </row>
-    <row r="1128" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1128" spans="3:3">
       <c r="C1128" s="2"/>
     </row>
-    <row r="1129" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1129" spans="3:3">
       <c r="C1129" s="2"/>
     </row>
-    <row r="1130" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1130" spans="3:3">
       <c r="C1130" s="2"/>
     </row>
-    <row r="1131" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1131" spans="3:3">
       <c r="C1131" s="2"/>
     </row>
-    <row r="1132" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1132" spans="3:3">
       <c r="C1132" s="2"/>
     </row>
-    <row r="1133" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1133" spans="3:3">
       <c r="C1133" s="2"/>
     </row>
-    <row r="1134" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1134" spans="3:3">
       <c r="C1134" s="2"/>
     </row>
-    <row r="1135" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1135" spans="3:3">
       <c r="C1135" s="2"/>
     </row>
-    <row r="1136" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1136" spans="3:3">
       <c r="C1136" s="2"/>
     </row>
-    <row r="1137" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1137" spans="3:3">
       <c r="C1137" s="2"/>
     </row>
-    <row r="1138" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1138" spans="3:3">
       <c r="C1138" s="2"/>
     </row>
-    <row r="1139" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1139" spans="3:3">
       <c r="C1139" s="2"/>
     </row>
-    <row r="1140" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1140" spans="3:3">
       <c r="C1140" s="2"/>
     </row>
-    <row r="1141" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1141" spans="3:3">
       <c r="C1141" s="2"/>
     </row>
-    <row r="1142" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1142" spans="3:3">
       <c r="C1142" s="2"/>
     </row>
-    <row r="1143" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1143" spans="3:3">
       <c r="C1143" s="2"/>
     </row>
-    <row r="1144" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1144" spans="3:3">
       <c r="C1144" s="2"/>
     </row>
-    <row r="1145" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1145" spans="3:3">
       <c r="C1145" s="2"/>
     </row>
-    <row r="1146" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1146" spans="3:3">
       <c r="C1146" s="2"/>
     </row>
-    <row r="1147" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1147" spans="3:3">
       <c r="C1147" s="2"/>
     </row>
-    <row r="1148" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1148" spans="3:3">
       <c r="C1148" s="2"/>
     </row>
-    <row r="1149" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1149" spans="3:3">
       <c r="C1149" s="2"/>
     </row>
-    <row r="1150" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1150" spans="3:3">
       <c r="C1150" s="2"/>
     </row>
-    <row r="1151" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1151" spans="3:3">
       <c r="C1151" s="2"/>
     </row>
-    <row r="1152" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1152" spans="3:3">
       <c r="C1152" s="2"/>
     </row>
-    <row r="1153" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1153" spans="3:3">
       <c r="C1153" s="2"/>
     </row>
-    <row r="1154" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1154" spans="3:3">
       <c r="C1154" s="2"/>
     </row>
-    <row r="1155" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1155" spans="3:3">
       <c r="C1155" s="2"/>
     </row>
-    <row r="1156" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1156" spans="3:3">
       <c r="C1156" s="2"/>
     </row>
-    <row r="1157" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1157" spans="3:3">
       <c r="C1157" s="2"/>
     </row>
-    <row r="1158" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1158" spans="3:3">
       <c r="C1158" s="2"/>
     </row>
-    <row r="1159" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1159" spans="3:3">
       <c r="C1159" s="2"/>
     </row>
-    <row r="1160" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1160" spans="3:3">
       <c r="C1160" s="2"/>
     </row>
-    <row r="1161" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1161" spans="3:3">
       <c r="C1161" s="2"/>
     </row>
-    <row r="1162" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1162" spans="3:3">
       <c r="C1162" s="2"/>
     </row>
-    <row r="1163" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1163" spans="3:3">
       <c r="C1163" s="2"/>
     </row>
-    <row r="1164" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1164" spans="3:3">
       <c r="C1164" s="2"/>
     </row>
-    <row r="1165" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1165" spans="3:3">
       <c r="C1165" s="2"/>
     </row>
-    <row r="1166" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1166" spans="3:3">
       <c r="C1166" s="2"/>
     </row>
-    <row r="1167" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1167" spans="3:3">
       <c r="C1167" s="2"/>
     </row>
-    <row r="1168" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1168" spans="3:3">
       <c r="C1168" s="2"/>
     </row>
-    <row r="1169" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1169" spans="3:3">
       <c r="C1169" s="2"/>
     </row>
-    <row r="1170" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1170" spans="3:3">
       <c r="C1170" s="2"/>
     </row>
-    <row r="1171" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1171" spans="3:3">
       <c r="C1171" s="2"/>
     </row>
-    <row r="1172" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1172" spans="3:3">
       <c r="C1172" s="2"/>
     </row>
-    <row r="1173" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1173" spans="3:3">
       <c r="C1173" s="2"/>
     </row>
-    <row r="1174" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1174" spans="3:3">
       <c r="C1174" s="2"/>
     </row>
-    <row r="1175" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1175" spans="3:3">
       <c r="C1175" s="2"/>
     </row>
-    <row r="1176" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1176" spans="3:3">
       <c r="C1176" s="2"/>
     </row>
-    <row r="1177" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1177" spans="3:3">
       <c r="C1177" s="2"/>
     </row>
-    <row r="1178" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1178" spans="3:3">
       <c r="C1178" s="2"/>
     </row>
-    <row r="1179" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1179" spans="3:3">
       <c r="C1179" s="2"/>
     </row>
-    <row r="1180" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1180" spans="3:3">
       <c r="C1180" s="2"/>
     </row>
-    <row r="1181" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1181" spans="3:3">
       <c r="C1181" s="2"/>
     </row>
-    <row r="1182" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1182" spans="3:3">
       <c r="C1182" s="2"/>
     </row>
-    <row r="1183" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1183" spans="3:3">
       <c r="C1183" s="2"/>
     </row>
-    <row r="1184" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1184" spans="3:3">
       <c r="C1184" s="2"/>
     </row>
-    <row r="1185" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1185" spans="3:3">
       <c r="C1185" s="2"/>
     </row>
-    <row r="1186" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1186" spans="3:3">
       <c r="C1186" s="2"/>
     </row>
-    <row r="1187" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1187" spans="3:3">
       <c r="C1187" s="2"/>
     </row>
-    <row r="1188" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1188" spans="3:3">
       <c r="C1188" s="2"/>
     </row>
-    <row r="1189" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1189" spans="3:3">
       <c r="C1189" s="2"/>
     </row>
-    <row r="1190" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1190" spans="3:3">
       <c r="C1190" s="2"/>
     </row>
-    <row r="1191" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1191" spans="3:3">
       <c r="C1191" s="2"/>
     </row>
-    <row r="1192" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1192" spans="3:3">
       <c r="C1192" s="2"/>
     </row>
-    <row r="1193" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1193" spans="3:3">
       <c r="C1193" s="2"/>
     </row>
-    <row r="1194" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1194" spans="3:3">
       <c r="C1194" s="2"/>
     </row>
-    <row r="1195" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1195" spans="3:3">
       <c r="C1195" s="2"/>
     </row>
-    <row r="1196" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1196" spans="3:3">
       <c r="C1196" s="2"/>
     </row>
-    <row r="1197" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1197" spans="3:3">
       <c r="C1197" s="2"/>
     </row>
-    <row r="1198" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1198" spans="3:3">
       <c r="C1198" s="2"/>
     </row>
-    <row r="1199" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1199" spans="3:3">
       <c r="C1199" s="2"/>
     </row>
-    <row r="1200" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1200" spans="3:3">
       <c r="C1200" s="2"/>
     </row>
-    <row r="1201" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1201" spans="3:3">
       <c r="C1201" s="2"/>
     </row>
-    <row r="1202" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1202" spans="3:3">
       <c r="C1202" s="2"/>
     </row>
-    <row r="1203" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1203" spans="3:3">
       <c r="C1203" s="2"/>
     </row>
-    <row r="1204" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1204" spans="3:3">
       <c r="C1204" s="2"/>
     </row>
-    <row r="1205" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1205" spans="3:3">
       <c r="C1205" s="2"/>
     </row>
-    <row r="1206" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1206" spans="3:3">
       <c r="C1206" s="2"/>
     </row>
-    <row r="1207" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1207" spans="3:3">
       <c r="C1207" s="2"/>
     </row>
-    <row r="1208" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1208" spans="3:3">
       <c r="C1208" s="2"/>
     </row>
-    <row r="1209" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1209" spans="3:3">
       <c r="C1209" s="2"/>
     </row>
-    <row r="1210" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1210" spans="3:3">
       <c r="C1210" s="2"/>
     </row>
-    <row r="1211" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1211" spans="3:3">
       <c r="C1211" s="2"/>
     </row>
-    <row r="1212" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1212" spans="3:3">
       <c r="C1212" s="2"/>
     </row>
-    <row r="1213" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1213" spans="3:3">
       <c r="C1213" s="2"/>
     </row>
-    <row r="1214" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1214" spans="3:3">
       <c r="C1214" s="2"/>
     </row>
-    <row r="1215" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1215" spans="3:3">
       <c r="C1215" s="2"/>
     </row>
-    <row r="1216" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1216" spans="3:3">
       <c r="C1216" s="2"/>
     </row>
-    <row r="1217" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1217" spans="3:3">
       <c r="C1217" s="2"/>
     </row>
-    <row r="1218" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1218" spans="3:3">
       <c r="C1218" s="2"/>
     </row>
-    <row r="1219" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1219" spans="3:3">
       <c r="C1219" s="2"/>
     </row>
-    <row r="1220" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1220" spans="3:3">
       <c r="C1220" s="2"/>
     </row>
-    <row r="1221" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1221" spans="3:3">
       <c r="C1221" s="2"/>
     </row>
-    <row r="1222" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1222" spans="3:3">
       <c r="C1222" s="2"/>
     </row>
-    <row r="1223" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1223" spans="3:3">
       <c r="C1223" s="2"/>
     </row>
-    <row r="1224" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1224" spans="3:3">
       <c r="C1224" s="2"/>
     </row>
-    <row r="1225" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1225" spans="3:3">
       <c r="C1225" s="2"/>
     </row>
-    <row r="1226" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1226" spans="3:3">
       <c r="C1226" s="2"/>
     </row>
-    <row r="1227" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1227" spans="3:3">
       <c r="C1227" s="2"/>
     </row>
-    <row r="1228" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1228" spans="3:3">
       <c r="C1228" s="2"/>
     </row>
-    <row r="1229" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1229" spans="3:3">
       <c r="C1229" s="2"/>
     </row>
-    <row r="1230" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1230" spans="3:3">
       <c r="C1230" s="2"/>
     </row>
-    <row r="1231" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1231" spans="3:3">
       <c r="C1231" s="2"/>
     </row>
-    <row r="1232" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1232" spans="3:3">
       <c r="C1232" s="2"/>
     </row>
-    <row r="1233" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1233" spans="3:3">
       <c r="C1233" s="2"/>
     </row>
-    <row r="1234" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1234" spans="3:3">
       <c r="C1234" s="2"/>
     </row>
-    <row r="1235" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1235" spans="3:3">
       <c r="C1235" s="2"/>
     </row>
-    <row r="1236" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1236" spans="3:3">
       <c r="C1236" s="2"/>
     </row>
-    <row r="1237" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1237" spans="3:3">
       <c r="C1237" s="2"/>
     </row>
-    <row r="1238" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1238" spans="3:3">
       <c r="C1238" s="2"/>
     </row>
-    <row r="1239" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1239" spans="3:3">
       <c r="C1239" s="2"/>
     </row>
-    <row r="1240" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1240" spans="3:3">
       <c r="C1240" s="2"/>
     </row>
-    <row r="1241" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1241" spans="3:3">
       <c r="C1241" s="2"/>
     </row>
-    <row r="1242" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1242" spans="3:3">
       <c r="C1242" s="2"/>
     </row>
-    <row r="1243" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1243" spans="3:3">
       <c r="C1243" s="2"/>
     </row>
-    <row r="1244" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1244" spans="3:3">
       <c r="C1244" s="2"/>
     </row>
-    <row r="1245" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1245" spans="3:3">
       <c r="C1245" s="2"/>
     </row>
-    <row r="1246" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1246" spans="3:3">
       <c r="C1246" s="2"/>
     </row>
-    <row r="1247" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1247" spans="3:3">
       <c r="C1247" s="2"/>
     </row>
-    <row r="1248" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1248" spans="3:3">
       <c r="C1248" s="2"/>
     </row>
-    <row r="1249" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1249" spans="3:3">
       <c r="C1249" s="2"/>
     </row>
-    <row r="1250" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1250" spans="3:3">
       <c r="C1250" s="2"/>
     </row>
-    <row r="1251" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1251" spans="3:3">
       <c r="C1251" s="2"/>
     </row>
-    <row r="1252" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1252" spans="3:3">
       <c r="C1252" s="2"/>
     </row>
-    <row r="1253" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1253" spans="3:3">
       <c r="C1253" s="2"/>
     </row>
-    <row r="1254" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1254" spans="3:3">
       <c r="C1254" s="2"/>
     </row>
-    <row r="1255" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1255" spans="3:3">
       <c r="C1255" s="2"/>
     </row>
-    <row r="1256" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1256" spans="3:3">
       <c r="C1256" s="2"/>
     </row>
-    <row r="1257" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1257" spans="3:3">
       <c r="C1257" s="2"/>
     </row>
-    <row r="1258" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1258" spans="3:3">
       <c r="C1258" s="2"/>
     </row>
-    <row r="1259" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1259" spans="3:3">
       <c r="C1259" s="2"/>
     </row>
-    <row r="1260" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1260" spans="3:3">
       <c r="C1260" s="2"/>
     </row>
-    <row r="1261" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1261" spans="3:3">
       <c r="C1261" s="2"/>
     </row>
-    <row r="1262" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1262" spans="3:3">
       <c r="C1262" s="2"/>
     </row>
-    <row r="1263" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1263" spans="3:3">
       <c r="C1263" s="2"/>
     </row>
-    <row r="1264" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1264" spans="3:3">
       <c r="C1264" s="2"/>
     </row>
-    <row r="1265" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1265" spans="3:3">
       <c r="C1265" s="2"/>
     </row>
-    <row r="1266" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1266" spans="3:3">
       <c r="C1266" s="2"/>
     </row>
-    <row r="1267" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1267" spans="3:3">
       <c r="C1267" s="2"/>
     </row>
-    <row r="1268" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1268" spans="3:3">
       <c r="C1268" s="2"/>
     </row>
-    <row r="1269" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1269" spans="3:3">
       <c r="C1269" s="2"/>
     </row>
-    <row r="1270" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1270" spans="3:3">
       <c r="C1270" s="2"/>
     </row>
-    <row r="1271" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1271" spans="3:3">
       <c r="C1271" s="2"/>
     </row>
-    <row r="1272" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1272" spans="3:3">
       <c r="C1272" s="2"/>
     </row>
-    <row r="1273" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1273" spans="3:3">
       <c r="C1273" s="2"/>
     </row>
-    <row r="1274" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1274" spans="3:3">
       <c r="C1274" s="2"/>
     </row>
-    <row r="1275" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1275" spans="3:3">
       <c r="C1275" s="2"/>
     </row>
-    <row r="1276" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1276" spans="3:3">
       <c r="C1276" s="2"/>
     </row>
-    <row r="1277" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1277" spans="3:3">
       <c r="C1277" s="2"/>
     </row>
-    <row r="1278" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1278" spans="3:3">
       <c r="C1278" s="2"/>
     </row>
-    <row r="1279" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1279" spans="3:3">
       <c r="C1279" s="2"/>
     </row>
-    <row r="1280" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1280" spans="3:3">
       <c r="C1280" s="2"/>
     </row>
-    <row r="1281" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1281" spans="3:3">
       <c r="C1281" s="2"/>
     </row>
-    <row r="1282" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1282" spans="3:3">
       <c r="C1282" s="2"/>
     </row>
-    <row r="1283" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1283" spans="3:3">
       <c r="C1283" s="2"/>
     </row>
-    <row r="1284" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1284" spans="3:3">
       <c r="C1284" s="2"/>
     </row>
-    <row r="1285" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1285" spans="3:3">
       <c r="C1285" s="2"/>
     </row>
-    <row r="1286" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1286" spans="3:3">
       <c r="C1286" s="2"/>
     </row>
-    <row r="1287" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1287" spans="3:3">
       <c r="C1287" s="2"/>
     </row>
-    <row r="1288" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1288" spans="3:3">
       <c r="C1288" s="2"/>
     </row>
-    <row r="1289" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1289" spans="3:3">
       <c r="C1289" s="2"/>
     </row>
-    <row r="1290" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1290" spans="3:3">
       <c r="C1290" s="2"/>
     </row>
-    <row r="1291" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1291" spans="3:3">
       <c r="C1291" s="2"/>
     </row>
-    <row r="1292" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1292" spans="3:3">
       <c r="C1292" s="2"/>
     </row>
-    <row r="1293" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1293" spans="3:3">
       <c r="C1293" s="2"/>
     </row>
-    <row r="1294" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1294" spans="3:3">
       <c r="C1294" s="2"/>
     </row>
-    <row r="1295" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1295" spans="3:3">
       <c r="C1295" s="2"/>
     </row>
-    <row r="1296" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1296" spans="3:3">
       <c r="C1296" s="2"/>
     </row>
-    <row r="1297" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1297" spans="3:3">
       <c r="C1297" s="2"/>
     </row>
-    <row r="1298" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1298" spans="3:3">
       <c r="C1298" s="2"/>
     </row>
-    <row r="1299" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1299" spans="3:3">
       <c r="C1299" s="2"/>
     </row>
-    <row r="1300" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1300" spans="3:3">
       <c r="C1300" s="2"/>
     </row>
-    <row r="1301" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1301" spans="3:3">
       <c r="C1301" s="2"/>
     </row>
-    <row r="1302" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1302" spans="3:3">
       <c r="C1302" s="2"/>
     </row>
-    <row r="1303" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1303" spans="3:3">
       <c r="C1303" s="2"/>
     </row>
-    <row r="1304" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1304" spans="3:3">
       <c r="C1304" s="2"/>
     </row>
-    <row r="1305" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1305" spans="3:3">
       <c r="C1305" s="2"/>
     </row>
-    <row r="1306" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1306" spans="3:3">
       <c r="C1306" s="2"/>
     </row>
-    <row r="1307" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1307" spans="3:3">
       <c r="C1307" s="2"/>
     </row>
-    <row r="1308" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1308" spans="3:3">
       <c r="C1308" s="2"/>
     </row>
-    <row r="1309" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1309" spans="3:3">
       <c r="C1309" s="2"/>
     </row>
-    <row r="1310" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1310" spans="3:3">
       <c r="C1310" s="2"/>
     </row>
-    <row r="1311" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1311" spans="3:3">
       <c r="C1311" s="2"/>
     </row>
-    <row r="1312" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1312" spans="3:3">
       <c r="C1312" s="2"/>
     </row>
-    <row r="1313" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1313" spans="3:3">
       <c r="C1313" s="2"/>
     </row>
-    <row r="1314" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1314" spans="3:3">
       <c r="C1314" s="2"/>
     </row>
-    <row r="1315" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1315" spans="3:3">
       <c r="C1315" s="2"/>
     </row>
-    <row r="1316" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1316" spans="3:3">
       <c r="C1316" s="2"/>
     </row>
-    <row r="1317" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1317" spans="3:3">
       <c r="C1317" s="2"/>
     </row>
-    <row r="1318" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1318" spans="3:3">
       <c r="C1318" s="2"/>
     </row>
-    <row r="1319" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1319" spans="3:3">
       <c r="C1319" s="2"/>
     </row>
-    <row r="1320" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1320" spans="3:3">
       <c r="C1320" s="2"/>
     </row>
-    <row r="1321" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1321" spans="3:3">
       <c r="C1321" s="2"/>
     </row>
-    <row r="1322" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1322" spans="3:3">
       <c r="C1322" s="2"/>
     </row>
-    <row r="1323" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1323" spans="3:3">
       <c r="C1323" s="2"/>
     </row>
-    <row r="1324" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1324" spans="3:3">
       <c r="C1324" s="2"/>
     </row>
-    <row r="1325" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1325" spans="3:3">
       <c r="C1325" s="2"/>
     </row>
-    <row r="1326" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1326" spans="3:3">
       <c r="C1326" s="2"/>
     </row>
-    <row r="1327" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1327" spans="3:3">
       <c r="C1327" s="2"/>
     </row>
-    <row r="1328" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1328" spans="3:3">
       <c r="C1328" s="2"/>
     </row>
-    <row r="1329" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1329" spans="3:3">
       <c r="C1329" s="2"/>
     </row>
-    <row r="1330" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1330" spans="3:3">
       <c r="C1330" s="2"/>
     </row>
-    <row r="1331" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1331" spans="3:3">
       <c r="C1331" s="2"/>
     </row>
-    <row r="1332" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1332" spans="3:3">
       <c r="C1332" s="2"/>
     </row>
-    <row r="1333" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1333" spans="3:3">
       <c r="C1333" s="2"/>
     </row>
-    <row r="1334" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1334" spans="3:3">
       <c r="C1334" s="2"/>
     </row>
-    <row r="1335" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1335" spans="3:3">
       <c r="C1335" s="2"/>
     </row>
-    <row r="1336" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1336" spans="3:3">
       <c r="C1336" s="2"/>
     </row>
-    <row r="1337" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1337" spans="3:3">
       <c r="C1337" s="2"/>
     </row>
-    <row r="1338" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1338" spans="3:3">
       <c r="C1338" s="2"/>
     </row>
-    <row r="1339" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1339" spans="3:3">
       <c r="C1339" s="2"/>
     </row>
-    <row r="1340" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1340" spans="3:3">
       <c r="C1340" s="2"/>
     </row>
-    <row r="1341" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1341" spans="3:3">
       <c r="C1341" s="2"/>
     </row>
-    <row r="1342" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1342" spans="3:3">
       <c r="C1342" s="2"/>
     </row>
-    <row r="1343" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1343" spans="3:3">
       <c r="C1343" s="2"/>
     </row>
-    <row r="1344" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1344" spans="3:3">
       <c r="C1344" s="2"/>
     </row>
-    <row r="1345" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1345" spans="3:3">
       <c r="C1345" s="2"/>
     </row>
-    <row r="1346" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1346" spans="3:3">
       <c r="C1346" s="2"/>
     </row>
-    <row r="1347" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1347" spans="3:3">
       <c r="C1347" s="2"/>
     </row>
-    <row r="1348" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1348" spans="3:3">
       <c r="C1348" s="2"/>
     </row>
-    <row r="1349" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1349" spans="3:3">
       <c r="C1349" s="2"/>
     </row>
-    <row r="1350" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1350" spans="3:3">
       <c r="C1350" s="2"/>
     </row>
-    <row r="1351" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1351" spans="3:3">
       <c r="C1351" s="2"/>
     </row>
-    <row r="1352" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1352" spans="3:3">
       <c r="C1352" s="2"/>
     </row>
-    <row r="1353" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1353" spans="3:3">
       <c r="C1353" s="2"/>
     </row>
-    <row r="1354" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1354" spans="3:3">
       <c r="C1354" s="2"/>
     </row>
-    <row r="1355" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1355" spans="3:3">
       <c r="C1355" s="2"/>
     </row>
-    <row r="1356" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1356" spans="3:3">
       <c r="C1356" s="2"/>
     </row>
-    <row r="1357" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1357" spans="3:3">
       <c r="C1357" s="2"/>
     </row>
-    <row r="1358" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1358" spans="3:3">
       <c r="C1358" s="2"/>
     </row>
-    <row r="1359" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1359" spans="3:3">
       <c r="C1359" s="2"/>
     </row>
-    <row r="1360" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1360" spans="3:3">
       <c r="C1360" s="2"/>
     </row>
-    <row r="1361" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1361" spans="3:3">
       <c r="C1361" s="2"/>
     </row>
-    <row r="1362" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1362" spans="3:3">
       <c r="C1362" s="2"/>
     </row>
-    <row r="1363" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1363" spans="3:3">
       <c r="C1363" s="2"/>
     </row>
-    <row r="1364" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1364" spans="3:3">
       <c r="C1364" s="2"/>
     </row>
-    <row r="1365" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1365" spans="3:3">
       <c r="C1365" s="2"/>
     </row>
-    <row r="1366" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1366" spans="3:3">
       <c r="C1366" s="2"/>
     </row>
-    <row r="1367" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1367" spans="3:3">
       <c r="C1367" s="2"/>
     </row>
-    <row r="1368" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1368" spans="3:3">
       <c r="C1368" s="2"/>
     </row>
-    <row r="1369" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1369" spans="3:3">
       <c r="C1369" s="2"/>
     </row>
-    <row r="1370" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1370" spans="3:3">
       <c r="C1370" s="2"/>
     </row>
-    <row r="1371" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1371" spans="3:3">
       <c r="C1371" s="2"/>
     </row>
-    <row r="1372" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1372" spans="3:3">
       <c r="C1372" s="2"/>
     </row>
-    <row r="1373" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1373" spans="3:3">
       <c r="C1373" s="2"/>
     </row>
-    <row r="1374" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1374" spans="3:3">
       <c r="C1374" s="2"/>
     </row>
-    <row r="1375" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1375" spans="3:3">
       <c r="C1375" s="2"/>
     </row>
-    <row r="1376" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1376" spans="3:3">
       <c r="C1376" s="2"/>
     </row>
-    <row r="1377" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1377" spans="3:3">
       <c r="C1377" s="2"/>
     </row>
-    <row r="1378" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1378" spans="3:3">
       <c r="C1378" s="2"/>
     </row>
-    <row r="1379" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1379" spans="3:3">
       <c r="C1379" s="2"/>
     </row>
-    <row r="1380" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1380" spans="3:3">
       <c r="C1380" s="2"/>
     </row>
-    <row r="1381" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1381" spans="3:3">
       <c r="C1381" s="2"/>
     </row>
-    <row r="1382" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1382" spans="3:3">
       <c r="C1382" s="2"/>
     </row>
-    <row r="1383" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1383" spans="3:3">
       <c r="C1383" s="2"/>
     </row>
-    <row r="1384" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1384" spans="3:3">
       <c r="C1384" s="2"/>
     </row>
-    <row r="1385" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1385" spans="3:3">
       <c r="C1385" s="2"/>
     </row>
-    <row r="1386" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1386" spans="3:3">
       <c r="C1386" s="2"/>
     </row>
-    <row r="1387" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1387" spans="3:3">
       <c r="C1387" s="2"/>
     </row>
-    <row r="1388" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1388" spans="3:3">
       <c r="C1388" s="2"/>
     </row>
-    <row r="1389" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1389" spans="3:3">
       <c r="C1389" s="2"/>
     </row>
-    <row r="1390" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1390" spans="3:3">
       <c r="C1390" s="2"/>
     </row>
-    <row r="1391" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1391" spans="3:3">
       <c r="C1391" s="2"/>
     </row>
-    <row r="1392" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1392" spans="3:3">
       <c r="C1392" s="2"/>
     </row>
-    <row r="1393" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1393" spans="3:3">
       <c r="C1393" s="2"/>
     </row>
-    <row r="1394" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1394" spans="3:3">
       <c r="C1394" s="2"/>
     </row>
-    <row r="1395" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1395" spans="3:3">
       <c r="C1395" s="2"/>
     </row>
-    <row r="1396" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1396" spans="3:3">
       <c r="C1396" s="2"/>
     </row>
-    <row r="1397" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1397" spans="3:3">
       <c r="C1397" s="2"/>
     </row>
-    <row r="1398" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1398" spans="3:3">
       <c r="C1398" s="2"/>
     </row>
-    <row r="1399" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1399" spans="3:3">
       <c r="C1399" s="2"/>
     </row>
-    <row r="1400" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1400" spans="3:3">
       <c r="C1400" s="2"/>
     </row>
-    <row r="1401" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1401" spans="3:3">
       <c r="C1401" s="2"/>
     </row>
-    <row r="1402" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1402" spans="3:3">
       <c r="C1402" s="2"/>
     </row>
-    <row r="1403" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1403" spans="3:3">
       <c r="C1403" s="2"/>
     </row>
-    <row r="1404" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1404" spans="3:3">
       <c r="C1404" s="2"/>
     </row>
-    <row r="1405" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1405" spans="3:3">
       <c r="C1405" s="2"/>
     </row>
-    <row r="1406" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1406" spans="3:3">
       <c r="C1406" s="2"/>
     </row>
-    <row r="1407" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1407" spans="3:3">
       <c r="C1407" s="2"/>
     </row>
-    <row r="1408" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1408" spans="3:3">
       <c r="C1408" s="2"/>
     </row>
-    <row r="1409" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1409" spans="3:3">
       <c r="C1409" s="2"/>
     </row>
-    <row r="1410" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1410" spans="3:3">
       <c r="C1410" s="2"/>
     </row>
-    <row r="1411" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1411" spans="3:3">
       <c r="C1411" s="2"/>
     </row>
-    <row r="1412" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1412" spans="3:3">
       <c r="C1412" s="2"/>
     </row>
-    <row r="1413" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1413" spans="3:3">
       <c r="C1413" s="2"/>
     </row>
-    <row r="1414" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1414" spans="3:3">
       <c r="C1414" s="2"/>
     </row>
-    <row r="1415" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1415" spans="3:3">
       <c r="C1415" s="2"/>
     </row>
-    <row r="1416" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1416" spans="3:3">
       <c r="C1416" s="2"/>
     </row>
-    <row r="1417" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1417" spans="3:3">
       <c r="C1417" s="2"/>
     </row>
-    <row r="1418" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1418" spans="3:3">
       <c r="C1418" s="2"/>
     </row>
-    <row r="1419" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1419" spans="3:3">
       <c r="C1419" s="2"/>
     </row>
-    <row r="1420" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1420" spans="3:3">
       <c r="C1420" s="2"/>
     </row>
-    <row r="1421" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1421" spans="3:3">
       <c r="C1421" s="2"/>
     </row>
-    <row r="1422" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1422" spans="3:3">
       <c r="C1422" s="2"/>
     </row>
-    <row r="1423" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1423" spans="3:3">
       <c r="C1423" s="2"/>
     </row>
-    <row r="1424" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1424" spans="3:3">
       <c r="C1424" s="2"/>
     </row>
-    <row r="1425" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1425" spans="3:3">
       <c r="C1425" s="2"/>
     </row>
-    <row r="1426" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1426" spans="3:3">
       <c r="C1426" s="2"/>
     </row>
-    <row r="1427" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1427" spans="3:3">
       <c r="C1427" s="2"/>
     </row>
-    <row r="1428" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1428" spans="3:3">
       <c r="C1428" s="2"/>
     </row>
-    <row r="1429" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1429" spans="3:3">
       <c r="C1429" s="2"/>
     </row>
-    <row r="1430" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1430" spans="3:3">
       <c r="C1430" s="2"/>
     </row>
-    <row r="1431" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1431" spans="3:3">
       <c r="C1431" s="2"/>
     </row>
-    <row r="1432" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1432" spans="3:3">
       <c r="C1432" s="2"/>
     </row>
-    <row r="1433" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1433" spans="3:3">
       <c r="C1433" s="2"/>
     </row>
-    <row r="1434" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1434" spans="3:3">
       <c r="C1434" s="2"/>
     </row>
-    <row r="1435" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1435" spans="3:3">
       <c r="C1435" s="2"/>
     </row>
-    <row r="1436" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1436" spans="3:3">
       <c r="C1436" s="2"/>
     </row>
-    <row r="1437" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1437" spans="3:3">
       <c r="C1437" s="2"/>
     </row>
-    <row r="1438" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1438" spans="3:3">
       <c r="C1438" s="2"/>
     </row>
-    <row r="1439" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1439" spans="3:3">
       <c r="C1439" s="2"/>
     </row>
-    <row r="1440" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1440" spans="3:3">
       <c r="C1440" s="2"/>
     </row>
-    <row r="1441" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1441" spans="3:3">
       <c r="C1441" s="2"/>
     </row>
-    <row r="1442" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1442" spans="3:3">
       <c r="C1442" s="2"/>
     </row>
-    <row r="1443" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1443" spans="3:3">
       <c r="C1443" s="2"/>
     </row>
-    <row r="1444" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1444" spans="3:3">
       <c r="C1444" s="2"/>
     </row>
-    <row r="1445" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1445" spans="3:3">
       <c r="C1445" s="2"/>
     </row>
-    <row r="1446" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1446" spans="3:3">
       <c r="C1446" s="2"/>
     </row>
-    <row r="1447" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1447" spans="3:3">
       <c r="C1447" s="2"/>
     </row>
-    <row r="1448" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1448" spans="3:3">
       <c r="C1448" s="2"/>
     </row>
-    <row r="1449" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1449" spans="3:3">
       <c r="C1449" s="2"/>
     </row>
-    <row r="1450" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1450" spans="3:3">
       <c r="C1450" s="2"/>
     </row>
-    <row r="1451" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1451" spans="3:3">
       <c r="C1451" s="2"/>
     </row>
-    <row r="1452" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1452" spans="3:3">
       <c r="C1452" s="2"/>
     </row>
-    <row r="1453" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1453" spans="3:3">
       <c r="C1453" s="2"/>
     </row>
-    <row r="1454" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1454" spans="3:3">
       <c r="C1454" s="2"/>
     </row>
-    <row r="1455" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1455" spans="3:3">
       <c r="C1455" s="2"/>
     </row>
-    <row r="1456" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1456" spans="3:3">
       <c r="C1456" s="2"/>
     </row>
-    <row r="1457" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1457" spans="3:3">
       <c r="C1457" s="2"/>
     </row>
-    <row r="1458" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1458" spans="3:3">
       <c r="C1458" s="2"/>
     </row>
-    <row r="1459" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1459" spans="3:3">
       <c r="C1459" s="2"/>
     </row>
-    <row r="1460" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1460" spans="3:3">
       <c r="C1460" s="2"/>
     </row>
-    <row r="1461" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1461" spans="3:3">
       <c r="C1461" s="2"/>
     </row>
-    <row r="1462" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1462" spans="3:3">
       <c r="C1462" s="2"/>
     </row>
-    <row r="1463" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1463" spans="3:3">
       <c r="C1463" s="2"/>
     </row>
-    <row r="1464" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1464" spans="3:3">
       <c r="C1464" s="2"/>
     </row>
-    <row r="1465" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1465" spans="3:3">
       <c r="C1465" s="2"/>
     </row>
-    <row r="1466" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1466" spans="3:3">
       <c r="C1466" s="2"/>
     </row>
-    <row r="1467" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1467" spans="3:3">
       <c r="C1467" s="2"/>
     </row>
-    <row r="1468" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1468" spans="3:3">
       <c r="C1468" s="2"/>
     </row>
-    <row r="1469" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1469" spans="3:3">
       <c r="C1469" s="2"/>
     </row>
-    <row r="1470" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1470" spans="3:3">
       <c r="C1470" s="2"/>
     </row>
-    <row r="1471" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1471" spans="3:3">
       <c r="C1471" s="2"/>
     </row>
-    <row r="1472" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1472" spans="3:3">
       <c r="C1472" s="2"/>
     </row>
-    <row r="1473" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1473" spans="3:3">
       <c r="C1473" s="2"/>
     </row>
-    <row r="1474" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1474" spans="3:3">
       <c r="C1474" s="2"/>
     </row>
-    <row r="1475" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1475" spans="3:3">
       <c r="C1475" s="2"/>
     </row>
-    <row r="1476" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1476" spans="3:3">
       <c r="C1476" s="2"/>
     </row>
-    <row r="1477" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1477" spans="3:3">
       <c r="C1477" s="2"/>
     </row>
-    <row r="1478" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1478" spans="3:3">
       <c r="C1478" s="2"/>
     </row>
-    <row r="1479" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1479" spans="3:3">
       <c r="C1479" s="2"/>
     </row>
-    <row r="1480" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1480" spans="3:3">
       <c r="C1480" s="2"/>
     </row>
-    <row r="1481" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1481" spans="3:3">
       <c r="C1481" s="2"/>
     </row>
-    <row r="1482" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1482" spans="3:3">
       <c r="C1482" s="2"/>
     </row>
-    <row r="1483" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1483" spans="3:3">
       <c r="C1483" s="2"/>
     </row>
-    <row r="1484" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1484" spans="3:3">
       <c r="C1484" s="2"/>
     </row>
-    <row r="1485" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1485" spans="3:3">
       <c r="C1485" s="2"/>
     </row>
-    <row r="1486" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1486" spans="3:3">
       <c r="C1486" s="2"/>
     </row>
-    <row r="1487" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1487" spans="3:3">
       <c r="C1487" s="2"/>
     </row>
-    <row r="1488" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1488" spans="3:3">
       <c r="C1488" s="2"/>
     </row>
-    <row r="1489" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1489" spans="3:3">
       <c r="C1489" s="2"/>
     </row>
-    <row r="1490" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1490" spans="3:3">
       <c r="C1490" s="2"/>
     </row>
-    <row r="1491" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1491" spans="3:3">
       <c r="C1491" s="2"/>
     </row>
-    <row r="1492" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1492" spans="3:3">
       <c r="C1492" s="2"/>
     </row>
-    <row r="1493" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1493" spans="3:3">
       <c r="C1493" s="2"/>
     </row>
-    <row r="1494" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1494" spans="3:3">
       <c r="C1494" s="2"/>
     </row>
-    <row r="1495" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1495" spans="3:3">
       <c r="C1495" s="2"/>
     </row>
-    <row r="1496" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1496" spans="3:3">
       <c r="C1496" s="2"/>
     </row>
-    <row r="1497" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1497" spans="3:3">
       <c r="C1497" s="2"/>
     </row>
-    <row r="1498" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1498" spans="3:3">
       <c r="C1498" s="2"/>
     </row>
-    <row r="1499" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1499" spans="3:3">
       <c r="C1499" s="2"/>
     </row>
-    <row r="1500" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1500" spans="3:3">
       <c r="C1500" s="2"/>
     </row>
-    <row r="1501" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1501" spans="3:3">
       <c r="C1501" s="2"/>
     </row>
-    <row r="1502" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1502" spans="3:3">
       <c r="C1502" s="2"/>
     </row>
-    <row r="1503" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1503" spans="3:3">
       <c r="C1503" s="2"/>
     </row>
-    <row r="1504" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1504" spans="3:3">
       <c r="C1504" s="2"/>
     </row>
-    <row r="1505" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1505" spans="3:3">
       <c r="C1505" s="2"/>
     </row>
-    <row r="1506" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1506" spans="3:3">
       <c r="C1506" s="2"/>
     </row>
-    <row r="1507" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1507" spans="3:3">
       <c r="C1507" s="2"/>
     </row>
-    <row r="1508" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1508" spans="3:3">
       <c r="C1508" s="2"/>
     </row>
-    <row r="1509" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1509" spans="3:3">
       <c r="C1509" s="2"/>
     </row>
-    <row r="1510" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1510" spans="3:3">
       <c r="C1510" s="2"/>
     </row>
-    <row r="1511" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1511" spans="3:3">
       <c r="C1511" s="2"/>
     </row>
-    <row r="1512" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1512" spans="3:3">
       <c r="C1512" s="2"/>
     </row>
-    <row r="1513" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1513" spans="3:3">
       <c r="C1513" s="2"/>
     </row>
-    <row r="1514" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1514" spans="3:3">
       <c r="C1514" s="2"/>
     </row>
-    <row r="1515" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1515" spans="3:3">
       <c r="C1515" s="2"/>
     </row>
-    <row r="1516" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1516" spans="3:3">
       <c r="C1516" s="2"/>
     </row>
-    <row r="1517" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1517" spans="3:3">
       <c r="C1517" s="2"/>
     </row>
-    <row r="1518" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1518" spans="3:3">
       <c r="C1518" s="2"/>
     </row>
-    <row r="1519" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1519" spans="3:3">
       <c r="C1519" s="2"/>
     </row>
-    <row r="1520" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1520" spans="3:3">
       <c r="C1520" s="2"/>
     </row>
-    <row r="1521" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1521" spans="3:3">
       <c r="C1521" s="2"/>
     </row>
-    <row r="1522" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1522" spans="3:3">
       <c r="C1522" s="2"/>
     </row>
-    <row r="1523" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1523" spans="3:3">
       <c r="C1523" s="2"/>
     </row>
-    <row r="1524" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1524" spans="3:3">
       <c r="C1524" s="2"/>
     </row>
-    <row r="1525" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1525" spans="3:3">
       <c r="C1525" s="2"/>
     </row>
-    <row r="1526" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1526" spans="3:3">
       <c r="C1526" s="2"/>
     </row>
-    <row r="1527" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1527" spans="3:3">
       <c r="C1527" s="2"/>
     </row>
-    <row r="1528" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1528" spans="3:3">
       <c r="C1528" s="2"/>
     </row>
-    <row r="1529" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1529" spans="3:3">
       <c r="C1529" s="2"/>
     </row>
-    <row r="1530" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1530" spans="3:3">
       <c r="C1530" s="2"/>
     </row>
-    <row r="1531" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1531" spans="3:3">
       <c r="C1531" s="2"/>
     </row>
-    <row r="1532" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1532" spans="3:3">
       <c r="C1532" s="2"/>
     </row>
-    <row r="1533" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1533" spans="3:3">
       <c r="C1533" s="2"/>
     </row>
-    <row r="1534" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1534" spans="3:3">
       <c r="C1534" s="2"/>
     </row>
-    <row r="1535" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1535" spans="3:3">
       <c r="C1535" s="2"/>
     </row>
-    <row r="1536" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1536" spans="3:3">
       <c r="C1536" s="2"/>
     </row>
-    <row r="1537" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1537" spans="3:3">
       <c r="C1537" s="2"/>
     </row>
-    <row r="1538" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1538" spans="3:3">
       <c r="C1538" s="2"/>
     </row>
-    <row r="1539" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1539" spans="3:3">
       <c r="C1539" s="2"/>
     </row>
-    <row r="1540" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1540" spans="3:3">
       <c r="C1540" s="2"/>
     </row>
-    <row r="1541" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1541" spans="3:3">
       <c r="C1541" s="2"/>
     </row>
-    <row r="1542" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1542" spans="3:3">
       <c r="C1542" s="2"/>
     </row>
-    <row r="1543" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1543" spans="3:3">
       <c r="C1543" s="2"/>
     </row>
-    <row r="1544" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1544" spans="3:3">
       <c r="C1544" s="2"/>
     </row>
-    <row r="1545" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1545" spans="3:3">
       <c r="C1545" s="2"/>
     </row>
-    <row r="1546" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1546" spans="3:3">
       <c r="C1546" s="2"/>
     </row>
-    <row r="1547" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1547" spans="3:3">
       <c r="C1547" s="2"/>
     </row>
-    <row r="1548" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1548" spans="3:3">
       <c r="C1548" s="2"/>
     </row>
-    <row r="1549" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1549" spans="3:3">
       <c r="C1549" s="2"/>
     </row>
-    <row r="1550" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1550" spans="3:3">
       <c r="C1550" s="2"/>
     </row>
-    <row r="1551" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1551" spans="3:3">
       <c r="C1551" s="2"/>
     </row>
-    <row r="1552" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1552" spans="3:3">
       <c r="C1552" s="2"/>
     </row>
-    <row r="1553" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1553" spans="3:3">
       <c r="C1553" s="2"/>
     </row>
-    <row r="1554" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1554" spans="3:3">
       <c r="C1554" s="2"/>
     </row>
-    <row r="1555" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1555" spans="3:3">
       <c r="C1555" s="2"/>
     </row>
-    <row r="1556" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1556" spans="3:3">
       <c r="C1556" s="2"/>
     </row>
-    <row r="1557" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1557" spans="3:3">
       <c r="C1557" s="2"/>
     </row>
-    <row r="1558" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1558" spans="3:3">
       <c r="C1558" s="2"/>
     </row>
-    <row r="1559" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1559" spans="3:3">
       <c r="C1559" s="2"/>
     </row>
-    <row r="1560" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1560" spans="3:3">
       <c r="C1560" s="2"/>
     </row>
-    <row r="1561" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1561" spans="3:3">
       <c r="C1561" s="2"/>
     </row>
-    <row r="1562" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1562" spans="3:3">
       <c r="C1562" s="2"/>
     </row>
-    <row r="1563" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1563" spans="3:3">
       <c r="C1563" s="2"/>
     </row>
-    <row r="1564" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1564" spans="3:3">
       <c r="C1564" s="2"/>
     </row>
-    <row r="1565" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1565" spans="3:3">
       <c r="C1565" s="2"/>
     </row>
-    <row r="1566" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1566" spans="3:3">
       <c r="C1566" s="2"/>
     </row>
-    <row r="1567" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1567" spans="3:3">
       <c r="C1567" s="2"/>
     </row>
-    <row r="1568" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1568" spans="3:3">
       <c r="C1568" s="2"/>
     </row>
-    <row r="1569" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1569" spans="3:3">
       <c r="C1569" s="2"/>
     </row>
-    <row r="1570" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1570" spans="3:3">
       <c r="C1570" s="2"/>
     </row>
-    <row r="1571" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1571" spans="3:3">
       <c r="C1571" s="2"/>
     </row>
-    <row r="1572" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1572" spans="3:3">
       <c r="C1572" s="2"/>
     </row>
-    <row r="1573" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1573" spans="3:3">
       <c r="C1573" s="2"/>
     </row>
-    <row r="1574" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1574" spans="3:3">
       <c r="C1574" s="2"/>
     </row>
-    <row r="1575" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1575" spans="3:3">
       <c r="C1575" s="2"/>
     </row>
-    <row r="1576" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1576" spans="3:3">
       <c r="C1576" s="2"/>
     </row>
-    <row r="1577" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1577" spans="3:3">
       <c r="C1577" s="2"/>
     </row>
-    <row r="1578" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1578" spans="3:3">
       <c r="C1578" s="2"/>
     </row>
-    <row r="1579" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1579" spans="3:3">
       <c r="C1579" s="2"/>
     </row>
-    <row r="1580" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1580" spans="3:3">
       <c r="C1580" s="2"/>
     </row>
-    <row r="1581" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1581" spans="3:3">
       <c r="C1581" s="2"/>
     </row>
-    <row r="1582" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1582" spans="3:3">
       <c r="C1582" s="2"/>
     </row>
-    <row r="1583" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1583" spans="3:3">
       <c r="C1583" s="2"/>
     </row>
-    <row r="1584" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1584" spans="3:3">
       <c r="C1584" s="2"/>
     </row>
-    <row r="1585" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1585" spans="3:3">
       <c r="C1585" s="2"/>
     </row>
-    <row r="1586" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1586" spans="3:3">
       <c r="C1586" s="2"/>
     </row>
-    <row r="1587" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1587" spans="3:3">
       <c r="C1587" s="2"/>
     </row>
-    <row r="1588" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1588" spans="3:3">
       <c r="C1588" s="2"/>
     </row>
-    <row r="1589" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1589" spans="3:3">
       <c r="C1589" s="2"/>
     </row>
-    <row r="1590" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1590" spans="3:3">
       <c r="C1590" s="2"/>
     </row>
-    <row r="1591" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1591" spans="3:3">
       <c r="C1591" s="2"/>
     </row>
-    <row r="1592" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1592" spans="3:3">
       <c r="C1592" s="2"/>
     </row>
-    <row r="1593" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1593" spans="3:3">
       <c r="C1593" s="2"/>
     </row>
-    <row r="1594" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1594" spans="3:3">
       <c r="C1594" s="2"/>
     </row>
-    <row r="1595" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1595" spans="3:3">
       <c r="C1595" s="2"/>
     </row>
-    <row r="1596" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1596" spans="3:3">
       <c r="C1596" s="2"/>
     </row>
-    <row r="1597" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1597" spans="3:3">
       <c r="C1597" s="2"/>
     </row>
-    <row r="1598" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1598" spans="3:3">
       <c r="C1598" s="2"/>
     </row>
-    <row r="1599" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1599" spans="3:3">
       <c r="C1599" s="2"/>
     </row>
-    <row r="1600" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1600" spans="3:3">
       <c r="C1600" s="2"/>
     </row>
-    <row r="1601" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1601" spans="3:3">
       <c r="C1601" s="2"/>
     </row>
-    <row r="1602" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1602" spans="3:3">
       <c r="C1602" s="2"/>
     </row>
-    <row r="1603" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1603" spans="3:3">
       <c r="C1603" s="2"/>
     </row>
-    <row r="1604" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1604" spans="3:3">
       <c r="C1604" s="2"/>
     </row>
-    <row r="1605" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1605" spans="3:3">
       <c r="C1605" s="2"/>
     </row>
-    <row r="1606" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1606" spans="3:3">
       <c r="C1606" s="2"/>
     </row>
-    <row r="1607" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1607" spans="3:3">
       <c r="C1607" s="2"/>
     </row>
-    <row r="1608" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1608" spans="3:3">
       <c r="C1608" s="2"/>
     </row>
-    <row r="1609" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1609" spans="3:3">
       <c r="C1609" s="2"/>
     </row>
-    <row r="1610" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1610" spans="3:3">
       <c r="C1610" s="2"/>
     </row>
-    <row r="1611" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1611" spans="3:3">
       <c r="C1611" s="2"/>
     </row>
-    <row r="1612" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1612" spans="3:3">
       <c r="C1612" s="2"/>
     </row>
-    <row r="1613" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1613" spans="3:3">
       <c r="C1613" s="2"/>
     </row>
-    <row r="1614" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1614" spans="3:3">
       <c r="C1614" s="2"/>
     </row>
-    <row r="1615" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1615" spans="3:3">
       <c r="C1615" s="2"/>
     </row>
-    <row r="1616" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1616" spans="3:3">
       <c r="C1616" s="2"/>
     </row>
-    <row r="1617" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1617" spans="3:3">
       <c r="C1617" s="2"/>
     </row>
-    <row r="1618" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1618" spans="3:3">
       <c r="C1618" s="2"/>
     </row>
-    <row r="1619" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1619" spans="3:3">
       <c r="C1619" s="2"/>
     </row>
-    <row r="1620" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1620" spans="3:3">
       <c r="C1620" s="2"/>
     </row>
-    <row r="1621" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1621" spans="3:3">
       <c r="C1621" s="2"/>
     </row>
-    <row r="1622" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1622" spans="3:3">
       <c r="C1622" s="2"/>
     </row>
-    <row r="1623" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1623" spans="3:3">
       <c r="C1623" s="2"/>
     </row>
-    <row r="1624" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1624" spans="3:3">
       <c r="C1624" s="2"/>
     </row>
-    <row r="1625" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1625" spans="3:3">
       <c r="C1625" s="2"/>
     </row>
-    <row r="1626" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1626" spans="3:3">
       <c r="C1626" s="2"/>
     </row>
-    <row r="1627" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1627" spans="3:3">
       <c r="C1627" s="2"/>
     </row>
-    <row r="1628" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1628" spans="3:3">
       <c r="C1628" s="2"/>
     </row>
-    <row r="1629" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1629" spans="3:3">
       <c r="C1629" s="2"/>
     </row>
-    <row r="1630" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1630" spans="3:3">
       <c r="C1630" s="2"/>
     </row>
-    <row r="1631" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1631" spans="3:3">
       <c r="C1631" s="2"/>
     </row>
-    <row r="1632" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1632" spans="3:3">
       <c r="C1632" s="2"/>
     </row>
-    <row r="1633" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1633" spans="3:3">
       <c r="C1633" s="2"/>
     </row>
-    <row r="1634" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1634" spans="3:3">
       <c r="C1634" s="2"/>
     </row>
-    <row r="1635" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1635" spans="3:3">
       <c r="C1635" s="2"/>
     </row>
-    <row r="1636" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1636" spans="3:3">
       <c r="C1636" s="2"/>
     </row>
-    <row r="1637" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1637" spans="3:3">
       <c r="C1637" s="2"/>
     </row>
-    <row r="1638" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1638" spans="3:3">
       <c r="C1638" s="2"/>
     </row>
-    <row r="1639" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1639" spans="3:3">
       <c r="C1639" s="2"/>
     </row>
-    <row r="1640" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1640" spans="3:3">
       <c r="C1640" s="2"/>
     </row>
-    <row r="1641" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1641" spans="3:3">
       <c r="C1641" s="2"/>
     </row>
-    <row r="1642" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1642" spans="3:3">
       <c r="C1642" s="2"/>
     </row>
-    <row r="1643" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1643" spans="3:3">
       <c r="C1643" s="2"/>
     </row>
-    <row r="1644" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1644" spans="3:3">
       <c r="C1644" s="2"/>
     </row>
-    <row r="1645" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1645" spans="3:3">
       <c r="C1645" s="2"/>
     </row>
-    <row r="1646" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1646" spans="3:3">
       <c r="C1646" s="2"/>
     </row>
-    <row r="1647" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1647" spans="3:3">
       <c r="C1647" s="2"/>
     </row>
-    <row r="1648" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1648" spans="3:3">
       <c r="C1648" s="2"/>
     </row>
-    <row r="1649" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1649" spans="3:3">
       <c r="C1649" s="2"/>
     </row>
-    <row r="1650" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1650" spans="3:3">
       <c r="C1650" s="2"/>
     </row>
-    <row r="1651" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1651" spans="3:3">
       <c r="C1651" s="2"/>
     </row>
-    <row r="1652" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1652" spans="3:3">
       <c r="C1652" s="2"/>
     </row>
-    <row r="1653" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1653" spans="3:3">
       <c r="C1653" s="2"/>
     </row>
-    <row r="1654" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1654" spans="3:3">
       <c r="C1654" s="2"/>
     </row>
-    <row r="1655" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1655" spans="3:3">
       <c r="C1655" s="2"/>
     </row>
-    <row r="1656" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1656" spans="3:3">
       <c r="C1656" s="2"/>
     </row>
-    <row r="1657" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1657" spans="3:3">
       <c r="C1657" s="2"/>
     </row>
-    <row r="1658" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1658" spans="3:3">
       <c r="C1658" s="2"/>
     </row>
-    <row r="1659" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1659" spans="3:3">
       <c r="C1659" s="2"/>
     </row>
-    <row r="1660" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1660" spans="3:3">
       <c r="C1660" s="2"/>
     </row>
-    <row r="1661" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1661" spans="3:3">
       <c r="C1661" s="2"/>
     </row>
-    <row r="1662" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1662" spans="3:3">
       <c r="C1662" s="2"/>
     </row>
-    <row r="1663" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1663" spans="3:3">
       <c r="C1663" s="2"/>
     </row>
-    <row r="1664" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1664" spans="3:3">
       <c r="C1664" s="2"/>
     </row>
-    <row r="1665" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1665" spans="3:3">
       <c r="C1665" s="2"/>
     </row>
-    <row r="1666" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1666" spans="3:3">
       <c r="C1666" s="2"/>
     </row>
-    <row r="1667" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1667" spans="3:3">
       <c r="C1667" s="2"/>
     </row>
-    <row r="1668" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1668" spans="3:3">
       <c r="C1668" s="2"/>
     </row>
-    <row r="1669" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1669" spans="3:3">
       <c r="C1669" s="2"/>
     </row>
-    <row r="1670" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1670" spans="3:3">
       <c r="C1670" s="2"/>
     </row>
-    <row r="1671" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1671" spans="3:3">
       <c r="C1671" s="2"/>
     </row>
-    <row r="1672" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1672" spans="3:3">
       <c r="C1672" s="2"/>
     </row>
-    <row r="1673" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1673" spans="3:3">
       <c r="C1673" s="2"/>
     </row>
-    <row r="1674" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1674" spans="3:3">
       <c r="C1674" s="2"/>
     </row>
-    <row r="1675" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1675" spans="3:3">
       <c r="C1675" s="2"/>
     </row>
-    <row r="1676" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1676" spans="3:3">
       <c r="C1676" s="2"/>
     </row>
-    <row r="1677" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1677" spans="3:3">
       <c r="C1677" s="2"/>
     </row>
-    <row r="1678" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1678" spans="3:3">
       <c r="C1678" s="2"/>
     </row>
-    <row r="1679" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1679" spans="3:3">
       <c r="C1679" s="2"/>
     </row>
-    <row r="1680" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1680" spans="3:3">
       <c r="C1680" s="2"/>
     </row>
-    <row r="1681" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1681" spans="3:3">
       <c r="C1681" s="2"/>
     </row>
-    <row r="1682" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1682" spans="3:3">
       <c r="C1682" s="2"/>
     </row>
-    <row r="1683" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1683" spans="3:3">
       <c r="C1683" s="2"/>
     </row>
-    <row r="1684" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1684" spans="3:3">
       <c r="C1684" s="2"/>
     </row>
-    <row r="1685" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1685" spans="3:3">
       <c r="C1685" s="2"/>
     </row>
-    <row r="1686" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1686" spans="3:3">
       <c r="C1686" s="2"/>
     </row>
-    <row r="1687" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1687" spans="3:3">
       <c r="C1687" s="2"/>
     </row>
-    <row r="1688" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1688" spans="3:3">
       <c r="C1688" s="2"/>
     </row>
-    <row r="1689" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1689" spans="3:3">
       <c r="C1689" s="2"/>
     </row>
-    <row r="1690" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1690" spans="3:3">
       <c r="C1690" s="2"/>
     </row>
-    <row r="1691" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1691" spans="3:3">
       <c r="C1691" s="2"/>
     </row>
-    <row r="1692" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1692" spans="3:3">
       <c r="C1692" s="2"/>
     </row>
-    <row r="1693" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1693" spans="3:3">
       <c r="C1693" s="2"/>
     </row>
-    <row r="1694" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1694" spans="3:3">
       <c r="C1694" s="2"/>
     </row>
-    <row r="1695" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1695" spans="3:3">
       <c r="C1695" s="2"/>
     </row>
-    <row r="1696" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1696" spans="3:3">
       <c r="C1696" s="2"/>
     </row>
-    <row r="1697" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1697" spans="3:3">
       <c r="C1697" s="2"/>
     </row>
-    <row r="1698" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1698" spans="3:3">
       <c r="C1698" s="2"/>
     </row>
-    <row r="1699" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1699" spans="3:3">
       <c r="C1699" s="2"/>
     </row>
-    <row r="1700" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1700" spans="3:3">
       <c r="C1700" s="2"/>
     </row>
-    <row r="1701" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1701" spans="3:3">
       <c r="C1701" s="2"/>
     </row>
-    <row r="1702" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1702" spans="3:3">
       <c r="C1702" s="2"/>
     </row>
-    <row r="1703" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1703" spans="3:3">
       <c r="C1703" s="2"/>
     </row>
-    <row r="1704" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1704" spans="3:3">
       <c r="C1704" s="2"/>
     </row>
-    <row r="1705" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1705" spans="3:3">
       <c r="C1705" s="2"/>
     </row>
-    <row r="1706" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1706" spans="3:3">
       <c r="C1706" s="2"/>
     </row>
-    <row r="1707" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1707" spans="3:3">
       <c r="C1707" s="2"/>
     </row>
-    <row r="1708" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1708" spans="3:3">
       <c r="C1708" s="2"/>
     </row>
-    <row r="1709" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1709" spans="3:3">
       <c r="C1709" s="2"/>
     </row>
-    <row r="1710" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1710" spans="3:3">
       <c r="C1710" s="2"/>
     </row>
-    <row r="1711" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1711" spans="3:3">
       <c r="C1711" s="2"/>
     </row>
-    <row r="1712" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1712" spans="3:3">
       <c r="C1712" s="2"/>
     </row>
-    <row r="1713" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1713" spans="3:3">
       <c r="C1713" s="2"/>
     </row>
-    <row r="1714" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1714" spans="3:3">
       <c r="C1714" s="2"/>
     </row>
-    <row r="1715" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1715" spans="3:3">
       <c r="C1715" s="2"/>
     </row>
-    <row r="1716" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1716" spans="3:3">
       <c r="C1716" s="2"/>
     </row>
-    <row r="1717" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1717" spans="3:3">
       <c r="C1717" s="2"/>
     </row>
-    <row r="1718" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1718" spans="3:3">
       <c r="C1718" s="2"/>
     </row>
-    <row r="1719" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1719" spans="3:3">
       <c r="C1719" s="2"/>
     </row>
-    <row r="1720" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1720" spans="3:3">
       <c r="C1720" s="2"/>
     </row>
-    <row r="1721" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1721" spans="3:3">
       <c r="C1721" s="2"/>
     </row>
-    <row r="1722" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1722" spans="3:3">
       <c r="C1722" s="2"/>
     </row>
-    <row r="1723" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1723" spans="3:3">
       <c r="C1723" s="2"/>
     </row>
-    <row r="1724" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1724" spans="3:3">
       <c r="C1724" s="2"/>
     </row>
-    <row r="1725" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1725" spans="3:3">
       <c r="C1725" s="2"/>
     </row>
-    <row r="1726" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1726" spans="3:3">
       <c r="C1726" s="2"/>
     </row>
-    <row r="1727" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1727" spans="3:3">
       <c r="C1727" s="2"/>
     </row>
-    <row r="1728" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1728" spans="3:3">
       <c r="C1728" s="2"/>
     </row>
-    <row r="1729" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1729" spans="3:3">
       <c r="C1729" s="2"/>
     </row>
-    <row r="1730" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1730" spans="3:3">
       <c r="C1730" s="2"/>
     </row>
-    <row r="1731" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1731" spans="3:3">
       <c r="C1731" s="2"/>
     </row>
-    <row r="1732" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1732" spans="3:3">
       <c r="C1732" s="2"/>
     </row>
-    <row r="1733" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1733" spans="3:3">
       <c r="C1733" s="2"/>
     </row>
-    <row r="1734" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1734" spans="3:3">
       <c r="C1734" s="2"/>
     </row>
-    <row r="1735" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1735" spans="3:3">
       <c r="C1735" s="2"/>
     </row>
-    <row r="1736" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1736" spans="3:3">
       <c r="C1736" s="2"/>
     </row>
-    <row r="1737" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1737" spans="3:3">
       <c r="C1737" s="2"/>
     </row>
-    <row r="1738" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1738" spans="3:3">
       <c r="C1738" s="2"/>
     </row>
-    <row r="1739" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1739" spans="3:3">
       <c r="C1739" s="2"/>
     </row>
-    <row r="1740" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1740" spans="3:3">
       <c r="C1740" s="2"/>
     </row>
-    <row r="1741" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1741" spans="3:3">
       <c r="C1741" s="2"/>
     </row>
-    <row r="1742" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1742" spans="3:3">
       <c r="C1742" s="2"/>
     </row>
-    <row r="1743" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1743" spans="3:3">
       <c r="C1743" s="2"/>
     </row>
-    <row r="1744" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1744" spans="3:3">
       <c r="C1744" s="2"/>
     </row>
-    <row r="1745" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1745" spans="3:3">
       <c r="C1745" s="2"/>
     </row>
-    <row r="1746" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1746" spans="3:3">
       <c r="C1746" s="2"/>
     </row>
-    <row r="1747" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1747" spans="3:3">
       <c r="C1747" s="2"/>
     </row>
-    <row r="1748" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1748" spans="3:3">
       <c r="C1748" s="2"/>
     </row>
-    <row r="1749" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1749" spans="3:3">
       <c r="C1749" s="2"/>
     </row>
-    <row r="1750" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1750" spans="3:3">
       <c r="C1750" s="2"/>
     </row>
-    <row r="1751" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1751" spans="3:3">
       <c r="C1751" s="2"/>
     </row>
-    <row r="1752" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1752" spans="3:3">
       <c r="C1752" s="2"/>
     </row>
-    <row r="1753" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1753" spans="3:3">
       <c r="C1753" s="2"/>
     </row>
-    <row r="1754" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1754" spans="3:3">
       <c r="C1754" s="2"/>
     </row>
-    <row r="1755" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1755" spans="3:3">
       <c r="C1755" s="2"/>
     </row>
-    <row r="1756" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1756" spans="3:3">
       <c r="C1756" s="2"/>
     </row>
-    <row r="1757" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1757" spans="3:3">
       <c r="C1757" s="2"/>
     </row>
-    <row r="1758" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1758" spans="3:3">
       <c r="C1758" s="2"/>
     </row>
-    <row r="1759" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1759" spans="3:3">
       <c r="C1759" s="2"/>
     </row>
-    <row r="1760" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1760" spans="3:3">
       <c r="C1760" s="2"/>
     </row>
-    <row r="1761" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1761" spans="3:3">
       <c r="C1761" s="2"/>
     </row>
-    <row r="1762" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1762" spans="3:3">
       <c r="C1762" s="2"/>
     </row>
-    <row r="1763" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1763" spans="3:3">
       <c r="C1763" s="2"/>
     </row>
-    <row r="1764" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1764" spans="3:3">
       <c r="C1764" s="2"/>
     </row>
-    <row r="1765" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1765" spans="3:3">
       <c r="C1765" s="2"/>
     </row>
-    <row r="1766" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1766" spans="3:3">
       <c r="C1766" s="2"/>
     </row>
-    <row r="1767" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1767" spans="3:3">
       <c r="C1767" s="2"/>
     </row>
-    <row r="1768" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1768" spans="3:3">
       <c r="C1768" s="2"/>
     </row>
-    <row r="1769" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1769" spans="3:3">
       <c r="C1769" s="2"/>
     </row>
-    <row r="1770" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1770" spans="3:3">
       <c r="C1770" s="2"/>
     </row>
-    <row r="1771" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1771" spans="3:3">
       <c r="C1771" s="2"/>
     </row>
-    <row r="1772" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1772" spans="3:3">
       <c r="C1772" s="2"/>
     </row>
-    <row r="1773" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1773" spans="3:3">
       <c r="C1773" s="2"/>
     </row>
-    <row r="1774" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1774" spans="3:3">
       <c r="C1774" s="2"/>
     </row>
-    <row r="1775" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1775" spans="3:3">
       <c r="C1775" s="2"/>
     </row>
-    <row r="1776" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1776" spans="3:3">
       <c r="C1776" s="2"/>
     </row>
-    <row r="1777" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1777" spans="3:3">
       <c r="C1777" s="2"/>
     </row>
-    <row r="1778" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1778" spans="3:3">
       <c r="C1778" s="2"/>
     </row>
-    <row r="1779" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1779" spans="3:3">
       <c r="C1779" s="2"/>
     </row>
-    <row r="1780" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1780" spans="3:3">
       <c r="C1780" s="2"/>
     </row>
-    <row r="1781" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1781" spans="3:3">
       <c r="C1781" s="2"/>
     </row>
-    <row r="1782" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1782" spans="3:3">
       <c r="C1782" s="2"/>
     </row>
-    <row r="1783" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1783" spans="3:3">
       <c r="C1783" s="2"/>
     </row>
-    <row r="1784" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1784" spans="3:3">
       <c r="C1784" s="2"/>
     </row>
-    <row r="1785" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1785" spans="3:3">
       <c r="C1785" s="2"/>
     </row>
-    <row r="1786" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1786" spans="3:3">
       <c r="C1786" s="2"/>
     </row>
-    <row r="1787" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1787" spans="3:3">
       <c r="C1787" s="2"/>
     </row>
-    <row r="1788" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1788" spans="3:3">
       <c r="C1788" s="2"/>
     </row>
-    <row r="1789" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1789" spans="3:3">
       <c r="C1789" s="2"/>
     </row>
-    <row r="1790" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1790" spans="3:3">
       <c r="C1790" s="2"/>
     </row>
-    <row r="1791" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1791" spans="3:3">
       <c r="C1791" s="2"/>
     </row>
-    <row r="1792" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1792" spans="3:3">
       <c r="C1792" s="2"/>
     </row>
-    <row r="1793" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1793" spans="3:3">
       <c r="C1793" s="2"/>
     </row>
-    <row r="1794" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1794" spans="3:3">
       <c r="C1794" s="2"/>
     </row>
-    <row r="1795" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1795" spans="3:3">
       <c r="C1795" s="2"/>
     </row>
-    <row r="1796" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1796" spans="3:3">
       <c r="C1796" s="2"/>
     </row>
-    <row r="1797" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1797" spans="3:3">
       <c r="C1797" s="2"/>
     </row>
-    <row r="1798" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1798" spans="3:3">
       <c r="C1798" s="2"/>
     </row>
-    <row r="1799" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1799" spans="3:3">
       <c r="C1799" s="2"/>
     </row>
-    <row r="1800" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1800" spans="3:3">
       <c r="C1800" s="2"/>
     </row>
-    <row r="1801" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1801" spans="3:3">
       <c r="C1801" s="2"/>
     </row>
-    <row r="1802" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1802" spans="3:3">
       <c r="C1802" s="2"/>
     </row>
-    <row r="1803" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1803" spans="3:3">
       <c r="C1803" s="2"/>
     </row>
-    <row r="1804" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1804" spans="3:3">
       <c r="C1804" s="2"/>
     </row>
-    <row r="1805" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1805" spans="3:3">
       <c r="C1805" s="2"/>
     </row>
-    <row r="1806" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1806" spans="3:3">
       <c r="C1806" s="2"/>
     </row>
-    <row r="1807" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1807" spans="3:3">
       <c r="C1807" s="2"/>
     </row>
-    <row r="1808" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1808" spans="3:3">
       <c r="C1808" s="2"/>
     </row>
-    <row r="1809" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1809" spans="3:3">
       <c r="C1809" s="2"/>
     </row>
-    <row r="1810" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1810" spans="3:3">
       <c r="C1810" s="2"/>
     </row>
-    <row r="1811" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1811" spans="3:3">
       <c r="C1811" s="2"/>
     </row>
-    <row r="1812" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1812" spans="3:3">
       <c r="C1812" s="2"/>
     </row>
-    <row r="1813" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1813" spans="3:3">
       <c r="C1813" s="2"/>
     </row>
-    <row r="1814" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1814" spans="3:3">
       <c r="C1814" s="2"/>
     </row>
-    <row r="1815" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1815" spans="3:3">
       <c r="C1815" s="2"/>
     </row>
-    <row r="1816" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1816" spans="3:3">
       <c r="C1816" s="2"/>
     </row>
-    <row r="1817" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1817" spans="3:3">
       <c r="C1817" s="2"/>
     </row>
-    <row r="1818" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1818" spans="3:3">
       <c r="C1818" s="2"/>
     </row>
-    <row r="1819" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1819" spans="3:3">
       <c r="C1819" s="2"/>
     </row>
-    <row r="1820" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1820" spans="3:3">
       <c r="C1820" s="2"/>
     </row>
-    <row r="1821" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1821" spans="3:3">
       <c r="C1821" s="2"/>
     </row>
-    <row r="1822" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1822" spans="3:3">
       <c r="C1822" s="2"/>
     </row>
-    <row r="1823" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1823" spans="3:3">
       <c r="C1823" s="2"/>
     </row>
-    <row r="1824" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1824" spans="3:3">
       <c r="C1824" s="2"/>
     </row>
-    <row r="1825" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1825" spans="3:3">
       <c r="C1825" s="2"/>
     </row>
-    <row r="1826" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1826" spans="3:3">
       <c r="C1826" s="2"/>
     </row>
-    <row r="1827" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1827" spans="3:3">
       <c r="C1827" s="2"/>
     </row>
-    <row r="1828" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1828" spans="3:3">
       <c r="C1828" s="2"/>
     </row>
-    <row r="1829" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1829" spans="3:3">
       <c r="C1829" s="2"/>
     </row>
-    <row r="1830" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1830" spans="3:3">
       <c r="C1830" s="2"/>
     </row>
-    <row r="1831" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1831" spans="3:3">
       <c r="C1831" s="2"/>
     </row>
-    <row r="1832" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1832" spans="3:3">
       <c r="C1832" s="2"/>
     </row>
-    <row r="1833" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1833" spans="3:3">
       <c r="C1833" s="2"/>
     </row>
-    <row r="1834" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1834" spans="3:3">
       <c r="C1834" s="2"/>
     </row>
-    <row r="1835" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1835" spans="3:3">
       <c r="C1835" s="2"/>
     </row>
-    <row r="1836" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1836" spans="3:3">
       <c r="C1836" s="2"/>
     </row>
-    <row r="1837" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1837" spans="3:3">
       <c r="C1837" s="2"/>
     </row>
-    <row r="1838" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1838" spans="3:3">
       <c r="C1838" s="2"/>
     </row>
-    <row r="1839" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1839" spans="3:3">
       <c r="C1839" s="2"/>
     </row>
-    <row r="1840" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1840" spans="3:3">
       <c r="C1840" s="2"/>
     </row>
-    <row r="1841" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1841" spans="3:3">
       <c r="C1841" s="2"/>
     </row>
-    <row r="1842" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1842" spans="3:3">
       <c r="C1842" s="2"/>
     </row>
-    <row r="1843" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1843" spans="3:3">
       <c r="C1843" s="2"/>
     </row>
-    <row r="1844" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1844" spans="3:3">
       <c r="C1844" s="2"/>
     </row>
-    <row r="1845" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1845" spans="3:3">
       <c r="C1845" s="2"/>
     </row>
-    <row r="1846" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1846" spans="3:3">
       <c r="C1846" s="2"/>
     </row>
-    <row r="1847" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1847" spans="3:3">
       <c r="C1847" s="2"/>
     </row>
-    <row r="1848" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1848" spans="3:3">
       <c r="C1848" s="2"/>
     </row>
-    <row r="1849" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1849" spans="3:3">
       <c r="C1849" s="2"/>
     </row>
-    <row r="1850" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1850" spans="3:3">
       <c r="C1850" s="2"/>
     </row>
-    <row r="1851" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1851" spans="3:3">
       <c r="C1851" s="2"/>
     </row>
-    <row r="1852" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1852" spans="3:3">
       <c r="C1852" s="2"/>
     </row>
-    <row r="1853" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1853" spans="3:3">
       <c r="C1853" s="2"/>
     </row>
-    <row r="1854" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1854" spans="3:3">
       <c r="C1854" s="2"/>
     </row>
-    <row r="1855" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1855" spans="3:3">
       <c r="C1855" s="2"/>
     </row>
-    <row r="1856" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1856" spans="3:3">
       <c r="C1856" s="2"/>
     </row>
-    <row r="1857" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1857" spans="3:3">
       <c r="C1857" s="2"/>
     </row>
-    <row r="1858" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1858" spans="3:3">
       <c r="C1858" s="2"/>
     </row>
-    <row r="1859" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1859" spans="3:3">
       <c r="C1859" s="2"/>
     </row>
-    <row r="1860" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1860" spans="3:3">
       <c r="C1860" s="2"/>
     </row>
-    <row r="1861" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1861" spans="3:3">
       <c r="C1861" s="2"/>
     </row>
-    <row r="1862" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1862" spans="3:3">
       <c r="C1862" s="2"/>
     </row>
-    <row r="1863" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1863" spans="3:3">
       <c r="C1863" s="2"/>
     </row>
-    <row r="1864" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1864" spans="3:3">
       <c r="C1864" s="2"/>
     </row>
-    <row r="1865" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1865" spans="3:3">
       <c r="C1865" s="2"/>
     </row>
-    <row r="1866" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1866" spans="3:3">
       <c r="C1866" s="2"/>
     </row>
-    <row r="1867" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1867" spans="3:3">
       <c r="C1867" s="2"/>
     </row>
-    <row r="1868" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1868" spans="3:3">
       <c r="C1868" s="2"/>
     </row>
-    <row r="1869" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1869" spans="3:3">
       <c r="C1869" s="2"/>
     </row>
-    <row r="1870" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1870" spans="3:3">
       <c r="C1870" s="2"/>
     </row>
-    <row r="1871" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1871" spans="3:3">
       <c r="C1871" s="2"/>
     </row>
-    <row r="1872" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1872" spans="3:3">
       <c r="C1872" s="2"/>
     </row>
-    <row r="1873" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1873" spans="3:3">
       <c r="C1873" s="2"/>
     </row>
-    <row r="1874" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1874" spans="3:3">
       <c r="C1874" s="2"/>
     </row>
-    <row r="1875" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1875" spans="3:3">
       <c r="C1875" s="2"/>
     </row>
-    <row r="1876" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1876" spans="3:3">
       <c r="C1876" s="2"/>
     </row>
-    <row r="1877" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1877" spans="3:3">
       <c r="C1877" s="2"/>
     </row>
-    <row r="1878" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1878" spans="3:3">
       <c r="C1878" s="2"/>
     </row>
-    <row r="1879" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1879" spans="3:3">
       <c r="C1879" s="2"/>
     </row>
-    <row r="1880" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1880" spans="3:3">
       <c r="C1880" s="2"/>
     </row>
-    <row r="1881" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1881" spans="3:3">
       <c r="C1881" s="2"/>
     </row>
-    <row r="1882" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1882" spans="3:3">
       <c r="C1882" s="2"/>
     </row>
-    <row r="1883" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1883" spans="3:3">
       <c r="C1883" s="2"/>
     </row>
-    <row r="1884" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1884" spans="3:3">
       <c r="C1884" s="2"/>
     </row>
-    <row r="1885" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1885" spans="3:3">
       <c r="C1885" s="2"/>
     </row>
-    <row r="1886" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1886" spans="3:3">
       <c r="C1886" s="2"/>
     </row>
-    <row r="1887" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1887" spans="3:3">
       <c r="C1887" s="2"/>
     </row>
-    <row r="1888" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1888" spans="3:3">
       <c r="C1888" s="2"/>
     </row>
-    <row r="1889" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1889" spans="3:3">
       <c r="C1889" s="2"/>
     </row>
-    <row r="1890" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1890" spans="3:3">
       <c r="C1890" s="2"/>
     </row>
-    <row r="1891" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1891" spans="3:3">
       <c r="C1891" s="2"/>
     </row>
-    <row r="1892" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1892" spans="3:3">
       <c r="C1892" s="2"/>
     </row>
-    <row r="1893" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1893" spans="3:3">
       <c r="C1893" s="2"/>
     </row>
-    <row r="1894" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1894" spans="3:3">
       <c r="C1894" s="2"/>
     </row>
-    <row r="1895" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1895" spans="3:3">
       <c r="C1895" s="2"/>
     </row>
-    <row r="1896" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1896" spans="3:3">
       <c r="C1896" s="2"/>
     </row>
-    <row r="1897" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1897" spans="3:3">
       <c r="C1897" s="2"/>
     </row>
-    <row r="1898" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1898" spans="3:3">
       <c r="C1898" s="2"/>
     </row>
-    <row r="1899" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1899" spans="3:3">
       <c r="C1899" s="2"/>
     </row>
-    <row r="1900" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1900" spans="3:3">
       <c r="C1900" s="2"/>
     </row>
-    <row r="1901" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1901" spans="3:3">
       <c r="C1901" s="2"/>
     </row>
-    <row r="1902" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1902" spans="3:3">
       <c r="C1902" s="2"/>
     </row>
-    <row r="1903" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1903" spans="3:3">
       <c r="C1903" s="2"/>
     </row>
-    <row r="1904" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1904" spans="3:3">
       <c r="C1904" s="2"/>
     </row>
-    <row r="1905" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1905" spans="3:3">
       <c r="C1905" s="2"/>
     </row>
-    <row r="1906" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1906" spans="3:3">
       <c r="C1906" s="2"/>
     </row>
-    <row r="1907" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1907" spans="3:3">
       <c r="C1907" s="2"/>
     </row>
-    <row r="1908" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1908" spans="3:3">
       <c r="C1908" s="2"/>
     </row>
-    <row r="1909" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1909" spans="3:3">
       <c r="C1909" s="2"/>
     </row>
-    <row r="1910" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1910" spans="3:3">
       <c r="C1910" s="2"/>
     </row>
-    <row r="1911" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1911" spans="3:3">
       <c r="C1911" s="2"/>
     </row>
-    <row r="1912" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1912" spans="3:3">
       <c r="C1912" s="2"/>
     </row>
-    <row r="1913" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1913" spans="3:3">
       <c r="C1913" s="2"/>
     </row>
-    <row r="1914" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1914" spans="3:3">
       <c r="C1914" s="2"/>
     </row>
-    <row r="1915" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1915" spans="3:3">
       <c r="C1915" s="2"/>
     </row>
-    <row r="1916" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1916" spans="3:3">
       <c r="C1916" s="2"/>
     </row>
-    <row r="1917" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1917" spans="3:3">
       <c r="C1917" s="2"/>
     </row>
-    <row r="1918" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1918" spans="3:3">
       <c r="C1918" s="2"/>
     </row>
-    <row r="1919" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1919" spans="3:3">
       <c r="C1919" s="2"/>
     </row>
-    <row r="1920" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1920" spans="3:3">
       <c r="C1920" s="2"/>
     </row>
-    <row r="1921" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1921" spans="3:3">
       <c r="C1921" s="2"/>
     </row>
-    <row r="1922" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1922" spans="3:3">
       <c r="C1922" s="2"/>
     </row>
-    <row r="1923" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1923" spans="3:3">
       <c r="C1923" s="2"/>
     </row>
-    <row r="1924" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1924" spans="3:3">
       <c r="C1924" s="2"/>
     </row>
-    <row r="1925" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1925" spans="3:3">
       <c r="C1925" s="2"/>
     </row>
-    <row r="1926" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1926" spans="3:3">
       <c r="C1926" s="2"/>
     </row>
-    <row r="1927" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1927" spans="3:3">
       <c r="C1927" s="2"/>
     </row>
-    <row r="1928" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1928" spans="3:3">
       <c r="C1928" s="2"/>
     </row>
-    <row r="1929" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1929" spans="3:3">
       <c r="C1929" s="2"/>
     </row>
-    <row r="1930" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1930" spans="3:3">
       <c r="C1930" s="2"/>
     </row>
-    <row r="1931" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1931" spans="3:3">
       <c r="C1931" s="2"/>
     </row>
-    <row r="1932" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1932" spans="3:3">
       <c r="C1932" s="2"/>
     </row>
-    <row r="1933" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1933" spans="3:3">
       <c r="C1933" s="2"/>
     </row>
-    <row r="1934" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1934" spans="3:3">
       <c r="C1934" s="2"/>
     </row>
-    <row r="1935" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1935" spans="3:3">
       <c r="C1935" s="2"/>
     </row>
-    <row r="1936" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1936" spans="3:3">
       <c r="C1936" s="2"/>
     </row>
-    <row r="1937" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1937" spans="3:3">
       <c r="C1937" s="2"/>
     </row>
-    <row r="1938" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1938" spans="3:3">
       <c r="C1938" s="2"/>
     </row>
-    <row r="1939" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1939" spans="3:3">
       <c r="C1939" s="2"/>
     </row>
-    <row r="1940" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1940" spans="3:3">
       <c r="C1940" s="2"/>
     </row>
-    <row r="1941" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1941" spans="3:3">
       <c r="C1941" s="2"/>
     </row>
-    <row r="1942" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1942" spans="3:3">
       <c r="C1942" s="2"/>
     </row>
-    <row r="1943" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1943" spans="3:3">
       <c r="C1943" s="2"/>
     </row>
-    <row r="1944" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1944" spans="3:3">
       <c r="C1944" s="2"/>
     </row>
-    <row r="1945" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1945" spans="3:3">
       <c r="C1945" s="2"/>
     </row>
-    <row r="1946" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1946" spans="3:3">
       <c r="C1946" s="2"/>
     </row>
-    <row r="1947" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1947" spans="3:3">
       <c r="C1947" s="2"/>
     </row>
-    <row r="1948" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1948" spans="3:3">
       <c r="C1948" s="2"/>
     </row>
-    <row r="1949" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1949" spans="3:3">
       <c r="C1949" s="2"/>
     </row>
-    <row r="1950" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1950" spans="3:3">
       <c r="C1950" s="2"/>
     </row>
-    <row r="1951" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1951" spans="3:3">
       <c r="C1951" s="2"/>
     </row>
-    <row r="1952" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1952" spans="3:3">
       <c r="C1952" s="2"/>
     </row>
-    <row r="1953" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1953" spans="3:3">
       <c r="C1953" s="2"/>
     </row>
-    <row r="1954" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1954" spans="3:3">
       <c r="C1954" s="2"/>
     </row>
-    <row r="1955" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1955" spans="3:3">
       <c r="C1955" s="2"/>
     </row>
-    <row r="1956" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1956" spans="3:3">
       <c r="C1956" s="2"/>
     </row>
-    <row r="1957" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1957" spans="3:3">
       <c r="C1957" s="2"/>
     </row>
-    <row r="1958" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1958" spans="3:3">
       <c r="C1958" s="2"/>
     </row>
-    <row r="1959" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1959" spans="3:3">
       <c r="C1959" s="2"/>
     </row>
-    <row r="1960" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1960" spans="3:3">
       <c r="C1960" s="2"/>
     </row>
-    <row r="1961" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1961" spans="3:3">
       <c r="C1961" s="2"/>
     </row>
-    <row r="1962" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1962" spans="3:3">
       <c r="C1962" s="2"/>
     </row>
-    <row r="1963" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1963" spans="3:3">
       <c r="C1963" s="2"/>
     </row>
-    <row r="1964" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1964" spans="3:3">
       <c r="C1964" s="2"/>
     </row>
-    <row r="1965" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1965" spans="3:3">
       <c r="C1965" s="2"/>
     </row>
-    <row r="1966" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1966" spans="3:3">
       <c r="C1966" s="2"/>
     </row>
-    <row r="1967" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1967" spans="3:3">
       <c r="C1967" s="2"/>
     </row>
-    <row r="1968" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1968" spans="3:3">
       <c r="C1968" s="2"/>
     </row>
-    <row r="1969" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1969" spans="3:3">
       <c r="C1969" s="2"/>
     </row>
-    <row r="1970" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1970" spans="3:3">
       <c r="C1970" s="2"/>
     </row>
-    <row r="1971" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1971" spans="3:3">
       <c r="C1971" s="2"/>
     </row>
-    <row r="1972" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1972" spans="3:3">
       <c r="C1972" s="2"/>
     </row>
-    <row r="1973" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1973" spans="3:3">
       <c r="C1973" s="2"/>
     </row>
-    <row r="1974" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1974" spans="3:3">
       <c r="C1974" s="2"/>
     </row>
-    <row r="1975" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1975" spans="3:3">
       <c r="C1975" s="2"/>
     </row>
-    <row r="1976" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1976" spans="3:3">
       <c r="C1976" s="2"/>
     </row>
-    <row r="1977" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1977" spans="3:3">
       <c r="C1977" s="2"/>
     </row>
-    <row r="1978" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1978" spans="3:3">
       <c r="C1978" s="2"/>
     </row>
-    <row r="1979" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1979" spans="3:3">
       <c r="C1979" s="2"/>
     </row>
-    <row r="1980" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1980" spans="3:3">
       <c r="C1980" s="2"/>
     </row>
-    <row r="1981" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1981" spans="3:3">
       <c r="C1981" s="2"/>
     </row>
-    <row r="1982" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1982" spans="3:3">
       <c r="C1982" s="2"/>
     </row>
-    <row r="1983" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1983" spans="3:3">
       <c r="C1983" s="2"/>
     </row>
-    <row r="1984" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1984" spans="3:3">
       <c r="C1984" s="2"/>
     </row>
-    <row r="1985" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1985" spans="3:3">
       <c r="C1985" s="2"/>
     </row>
-    <row r="1986" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1986" spans="3:3">
       <c r="C1986" s="2"/>
     </row>
-    <row r="1987" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1987" spans="3:3">
       <c r="C1987" s="2"/>
     </row>
-    <row r="1988" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1988" spans="3:3">
       <c r="C1988" s="2"/>
     </row>
-    <row r="1989" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1989" spans="3:3">
       <c r="C1989" s="2"/>
     </row>
-    <row r="1990" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1990" spans="3:3">
       <c r="C1990" s="2"/>
     </row>
-    <row r="1991" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1991" spans="3:3">
       <c r="C1991" s="2"/>
     </row>
-    <row r="1992" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1992" spans="3:3">
       <c r="C1992" s="2"/>
     </row>
-    <row r="1993" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1993" spans="3:3">
       <c r="C1993" s="2"/>
     </row>
-    <row r="1994" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1994" spans="3:3">
       <c r="C1994" s="2"/>
     </row>
-    <row r="1995" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1995" spans="3:3">
       <c r="C1995" s="2"/>
     </row>
-    <row r="1996" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1996" spans="3:3">
       <c r="C1996" s="2"/>
     </row>
-    <row r="1997" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1997" spans="3:3">
       <c r="C1997" s="2"/>
     </row>
-    <row r="1998" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1998" spans="3:3">
       <c r="C1998" s="2"/>
     </row>
-    <row r="1999" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="1999" spans="3:3">
       <c r="C1999" s="2"/>
     </row>
-    <row r="2000" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2000" spans="3:3">
       <c r="C2000" s="2"/>
     </row>
-    <row r="2001" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="2001" spans="3:3">
       <c r="C2001" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D2001" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D2001">
+    <sortState ref="A2:D2001">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18.75">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>8</v>
       </c>
